--- a/Fischer_Tropsch/FischerTropsch_Naphta_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Naphta_Greenfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Greenfield_Patagonien_Naphta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F256EDD-1E1C-4398-8D7F-4C54367D73A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8CDC9E-9129-46F1-B107-93D0C9AE9AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -473,9 +473,6 @@
     <t>€/kWa</t>
   </si>
   <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
     <t>(%_Kapa)/h</t>
   </si>
   <si>
@@ -758,9 +755,6 @@
     <t>kW_el</t>
   </si>
   <si>
-    <t>€ h / kg a</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -1374,6 +1368,12 @@
   </si>
   <si>
     <t>kWh_th/a</t>
+  </si>
+  <si>
+    <t>€/ kg a</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -1734,23 +1734,32 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1758,26 +1767,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1788,11 +1782,17 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2359,7 +2359,7 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2429,19 +2429,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="74"/>
       <c r="B8" s="84" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E8" s="66">
         <v>38.99</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2451,7 +2451,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E9" s="65">
         <v>285.39999999999998</v>
@@ -2467,13 +2467,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E10" s="65">
         <v>2440</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2483,7 +2483,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E11" s="64">
         <v>0.03</v>
@@ -2499,45 +2499,45 @@
         <v>86</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E12" s="65">
         <v>0.63</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="74"/>
       <c r="B13" s="85"/>
       <c r="C13" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E13" s="65">
         <v>4.8600000000000003</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="74"/>
       <c r="B14" s="85"/>
       <c r="C14" s="13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E14" s="65">
         <v>0.39</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2547,7 +2547,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E15" s="62">
         <v>20</v>
@@ -2563,7 +2563,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E16" s="63">
         <v>7.0000000000000007E-2</v>
@@ -2575,13 +2575,13 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="74"/>
       <c r="B17" s="88" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C17" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E17" s="53">
         <v>3.7</v>
@@ -2597,13 +2597,13 @@
         <v>84</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E18" s="54">
         <v>0.27</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2613,13 +2613,13 @@
         <v>10</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E19" s="54">
         <v>700</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2629,7 +2629,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E20" s="54">
         <v>0.02</v>
@@ -2645,7 +2645,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E21" s="54">
         <v>20</v>
@@ -2661,7 +2661,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E22" s="55">
         <v>0.05</v>
@@ -2673,35 +2673,35 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="74"/>
       <c r="B23" s="87" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C23" s="44" t="s">
         <v>84</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E23" s="46">
         <v>0.5</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="74"/>
       <c r="B24" s="87"/>
       <c r="C24" s="44" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E24" s="46">
         <v>1.75</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2711,13 +2711,13 @@
         <v>10</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E25" s="46">
         <v>7000</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2727,7 +2727,7 @@
         <v>11</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E26" s="47">
         <v>0.05</v>
@@ -2743,7 +2743,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E27" s="48">
         <v>15</v>
@@ -2759,7 +2759,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E28" s="47">
         <v>7.0000000000000007E-2</v>
@@ -2785,7 +2785,7 @@
         <v>490</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2833,7 +2833,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2897,25 +2897,25 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="74"/>
       <c r="B37" s="79" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C37" s="26" t="s">
         <v>87</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E37" s="38">
         <v>2.83</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2925,7 +2925,7 @@
         <v>11</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E38" s="33">
         <v>0.03</v>
@@ -2941,7 +2941,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E39" s="34">
         <v>30</v>
@@ -2957,13 +2957,13 @@
         <v>20</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E40" s="33">
         <v>7.3999999999999999E-4</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2973,7 +2973,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E41" s="33">
         <v>0.98</v>
@@ -2989,7 +2989,7 @@
         <v>36</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E42" s="33">
         <v>0.98</v>
@@ -3005,7 +3005,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E43" s="33">
         <v>0.05</v>
@@ -3021,19 +3021,19 @@
         <v>88</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E44" s="37">
         <v>0</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="74"/>
       <c r="B45" s="79" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>91</v>
@@ -3045,7 +3045,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -3464,19 +3464,19 @@
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="74"/>
       <c r="B71" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C71" t="s">
+        <v>289</v>
+      </c>
+      <c r="D71" t="s">
         <v>290</v>
-      </c>
-      <c r="C71" t="s">
-        <v>291</v>
-      </c>
-      <c r="D71" t="s">
-        <v>292</v>
       </c>
       <c r="E71" s="7">
         <v>-1E-4</v>
       </c>
       <c r="F71" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3500,38 +3500,38 @@
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="74"/>
       <c r="B73" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="69" t="s">
+        <v>372</v>
+      </c>
+      <c r="D73" s="69" t="s">
         <v>373</v>
-      </c>
-      <c r="C73" s="69" t="s">
-        <v>374</v>
-      </c>
-      <c r="D73" s="69" t="s">
-        <v>375</v>
       </c>
       <c r="E73" s="19">
         <v>-0.55000000000000004</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="75"/>
       <c r="B74" s="61" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E74" s="67">
         <f>-2.2</f>
         <v>-2.2000000000000002</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3591,31 +3591,31 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="95" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>97</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>98</v>
       </c>
       <c r="E2" s="30"/>
       <c r="F2" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="92"/>
+      <c r="A3" s="99"/>
       <c r="B3" s="89"/>
       <c r="C3" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="13" t="s">
@@ -3623,402 +3623,402 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="92"/>
+      <c r="A4" s="99"/>
       <c r="B4" s="89"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="92"/>
+      <c r="A5" s="99"/>
       <c r="B5" s="89"/>
       <c r="C5" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E5" s="33"/>
       <c r="F5" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="92"/>
+      <c r="A6" s="99"/>
       <c r="B6" s="89"/>
       <c r="C6" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="92"/>
+      <c r="A7" s="99"/>
       <c r="B7" s="89"/>
       <c r="C7" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="92"/>
+      <c r="A8" s="99"/>
       <c r="B8" s="89"/>
       <c r="C8" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="92"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="89"/>
       <c r="C9" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E9" s="34"/>
       <c r="F9" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="92"/>
+      <c r="A10" s="99"/>
       <c r="B10" s="89"/>
       <c r="C10" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="92"/>
+      <c r="A11" s="99"/>
       <c r="B11" s="89"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="92"/>
-      <c r="B12" s="94" t="s">
-        <v>366</v>
+      <c r="A12" s="99"/>
+      <c r="B12" s="107" t="s">
+        <v>364</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E12" s="68"/>
       <c r="F12" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="92"/>
-      <c r="B13" s="95"/>
+      <c r="A13" s="99"/>
+      <c r="B13" s="97"/>
       <c r="C13" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="92"/>
-      <c r="B14" s="95"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="97"/>
       <c r="C14" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="92"/>
-      <c r="B15" s="95"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="97"/>
       <c r="C15" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="92"/>
-      <c r="B16" s="95"/>
+      <c r="A16" s="99"/>
+      <c r="B16" s="97"/>
       <c r="C16" s="13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E16" s="33"/>
       <c r="F16" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="92"/>
-      <c r="B17" s="95"/>
+      <c r="A17" s="99"/>
+      <c r="B17" s="97"/>
       <c r="C17" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="92"/>
-      <c r="B18" s="95"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="97"/>
       <c r="C18" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="92"/>
-      <c r="B19" s="95"/>
+      <c r="A19" s="99"/>
+      <c r="B19" s="97"/>
       <c r="C19" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="92"/>
-      <c r="B20" s="95"/>
+      <c r="A20" s="99"/>
+      <c r="B20" s="97"/>
       <c r="C20" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="92"/>
-      <c r="B21" s="95"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="97"/>
       <c r="C21" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="92"/>
-      <c r="B22" s="95"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="92"/>
-      <c r="B23" s="96"/>
+      <c r="A23" s="99"/>
+      <c r="B23" s="108"/>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
       <c r="F23" s="36"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
+      <c r="A24" s="99"/>
       <c r="B24" s="88" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="13" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="92"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="89"/>
       <c r="C25" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E25" s="31"/>
       <c r="F25" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
+      <c r="A26" s="99"/>
       <c r="B26" s="89"/>
       <c r="C26" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E26" s="33"/>
       <c r="F26" s="13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="92"/>
+      <c r="A27" s="99"/>
       <c r="B27" s="89"/>
       <c r="C27" s="13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="92"/>
+      <c r="A28" s="99"/>
       <c r="B28" s="89"/>
       <c r="C28" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E28" s="34"/>
       <c r="F28" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="92"/>
+      <c r="A29" s="99"/>
       <c r="B29" s="89"/>
       <c r="C29" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E29" s="34"/>
       <c r="F29" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="92"/>
+      <c r="A30" s="99"/>
       <c r="B30" s="89"/>
       <c r="C30" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E30" s="34"/>
       <c r="F30" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="92"/>
+      <c r="A31" s="99"/>
       <c r="B31" s="89"/>
       <c r="C31" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E31" s="33"/>
       <c r="F31" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
+      <c r="A32" s="99"/>
       <c r="B32" s="89"/>
       <c r="C32" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E32" s="33"/>
       <c r="F32" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
+      <c r="A33" s="99"/>
       <c r="B33" s="90"/>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
@@ -4026,475 +4026,475 @@
       <c r="F33" s="36"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="92"/>
+      <c r="A34" s="99"/>
       <c r="B34" s="87" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E34" s="31"/>
       <c r="F34" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="92"/>
+      <c r="A35" s="99"/>
       <c r="B35" s="87"/>
       <c r="C35" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E35" s="31"/>
       <c r="F35" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="92"/>
+      <c r="A36" s="99"/>
       <c r="B36" s="87"/>
       <c r="C36" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E36" s="33"/>
       <c r="F36" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
+      <c r="A37" s="99"/>
       <c r="B37" s="87"/>
       <c r="C37" s="13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E37" s="33"/>
       <c r="F37" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="92"/>
+      <c r="A38" s="99"/>
       <c r="B38" s="87"/>
       <c r="C38" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+      <c r="A39" s="99"/>
       <c r="B39" s="87"/>
       <c r="C39" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E39" s="34"/>
       <c r="F39" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="92"/>
+      <c r="A40" s="99"/>
       <c r="B40" s="87"/>
       <c r="C40" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E40" s="34"/>
       <c r="F40" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="92"/>
+      <c r="A41" s="99"/>
       <c r="B41" s="87"/>
       <c r="C41" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E41" s="34"/>
       <c r="F41" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="92"/>
+      <c r="A42" s="99"/>
       <c r="B42" s="87"/>
       <c r="C42" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E42" s="33"/>
       <c r="F42" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="92"/>
+      <c r="A43" s="99"/>
       <c r="B43" s="87"/>
       <c r="C43" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E43" s="33"/>
       <c r="F43" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="92"/>
+      <c r="A44" s="99"/>
       <c r="B44" s="87"/>
       <c r="E44" s="33"/>
     </row>
     <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="91" t="s">
+      <c r="A45" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="100" t="s">
+      <c r="B45" s="110" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="2" t="s">
-        <v>188</v>
+        <v>392</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="92"/>
+      <c r="A46" s="99"/>
       <c r="B46" s="87"/>
       <c r="C46" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E46" s="33"/>
       <c r="F46" t="s">
-        <v>30</v>
+        <v>393</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="92"/>
+      <c r="A47" s="99"/>
       <c r="B47" s="87"/>
       <c r="C47" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E47" s="34"/>
       <c r="F47" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="92"/>
+      <c r="A48" s="99"/>
       <c r="B48" s="87"/>
       <c r="C48" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E48" s="33"/>
       <c r="F48" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="92"/>
+      <c r="A49" s="99"/>
       <c r="B49" s="87"/>
       <c r="C49" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E49" s="33"/>
       <c r="F49" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="92"/>
+      <c r="A50" s="99"/>
       <c r="B50" s="87"/>
       <c r="C50" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E50" s="33"/>
       <c r="F50" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="92"/>
+      <c r="A51" s="99"/>
       <c r="B51" s="87"/>
       <c r="C51" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E51" s="33"/>
       <c r="F51" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="92"/>
+      <c r="A52" s="99"/>
       <c r="B52" s="87"/>
       <c r="C52" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E52" s="33"/>
       <c r="F52" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="92"/>
+      <c r="A53" s="99"/>
       <c r="B53" s="87"/>
       <c r="C53" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E53" s="33"/>
       <c r="F53" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="92"/>
-      <c r="B54" s="101"/>
+      <c r="A54" s="99"/>
+      <c r="B54" s="102"/>
       <c r="C54" s="36"/>
       <c r="D54" s="36"/>
       <c r="E54" s="37"/>
       <c r="F54" s="36"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="92"/>
+      <c r="A55" s="99"/>
       <c r="B55" s="87" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E55" s="31"/>
       <c r="F55" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="92"/>
+      <c r="A56" s="99"/>
       <c r="B56" s="87"/>
       <c r="C56" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E56" s="33"/>
       <c r="F56" s="13" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="92"/>
+      <c r="A57" s="99"/>
       <c r="B57" s="87"/>
       <c r="C57" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E57" s="34"/>
       <c r="F57" s="13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="92"/>
+      <c r="A58" s="99"/>
       <c r="B58" s="87"/>
       <c r="C58" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E58" s="33"/>
       <c r="F58" s="13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="92"/>
+      <c r="A59" s="99"/>
       <c r="B59" s="87"/>
       <c r="C59" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E59" s="33"/>
       <c r="F59" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="92"/>
+      <c r="A60" s="99"/>
       <c r="B60" s="87"/>
       <c r="C60" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E60" s="33"/>
       <c r="F60" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="92"/>
+      <c r="A61" s="99"/>
       <c r="B61" s="87"/>
       <c r="C61" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E61" s="33"/>
       <c r="F61" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="92"/>
+      <c r="A62" s="99"/>
       <c r="B62" s="87"/>
       <c r="C62" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E62" s="33"/>
       <c r="F62" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="92"/>
+      <c r="A63" s="99"/>
       <c r="B63" s="87"/>
       <c r="C63" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E63" s="33"/>
       <c r="F63" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="92"/>
-      <c r="B64" s="101"/>
+      <c r="A64" s="99"/>
+      <c r="B64" s="102"/>
       <c r="E64" s="33"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="92"/>
-      <c r="B65" s="98" t="s">
+      <c r="A65" s="99"/>
+      <c r="B65" s="101" t="s">
         <v>6</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E65" s="39"/>
       <c r="F65" s="35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="92"/>
+      <c r="A66" s="99"/>
       <c r="B66" s="87"/>
       <c r="C66" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E66" s="33"/>
       <c r="F66" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="92"/>
+      <c r="A67" s="99"/>
       <c r="B67" s="89"/>
       <c r="C67" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D67" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="E67" s="31"/>
       <c r="F67" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="92"/>
+      <c r="A68" s="99"/>
       <c r="B68" s="89"/>
       <c r="C68" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E68" s="31"/>
       <c r="F68" s="13" t="s">
@@ -4502,172 +4502,172 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="92"/>
+      <c r="A69" s="99"/>
       <c r="B69" s="89"/>
       <c r="C69" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E69" s="31"/>
       <c r="F69" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="92"/>
+      <c r="A70" s="99"/>
       <c r="B70" s="89"/>
       <c r="C70" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E70" s="33"/>
       <c r="F70" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="92"/>
+      <c r="A71" s="99"/>
       <c r="B71" s="89"/>
       <c r="C71" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E71" s="31"/>
       <c r="F71" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="92"/>
+      <c r="A72" s="99"/>
       <c r="B72" s="89"/>
       <c r="C72" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E72" s="33"/>
       <c r="F72" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="92"/>
+      <c r="A73" s="99"/>
       <c r="B73" s="89"/>
       <c r="C73" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E73" s="33"/>
       <c r="F73" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="92"/>
+      <c r="A74" s="99"/>
       <c r="B74" s="89"/>
       <c r="C74" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E74" s="33"/>
       <c r="F74" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="92"/>
+      <c r="A75" s="99"/>
       <c r="B75" s="89"/>
       <c r="C75" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E75" s="33"/>
       <c r="F75" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="97"/>
-      <c r="B76" s="99"/>
+      <c r="A76" s="100"/>
+      <c r="B76" s="109"/>
       <c r="C76" s="40"/>
       <c r="D76" s="40"/>
       <c r="E76" s="41"/>
       <c r="F76" s="40"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="91" t="s">
+      <c r="A77" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="93" t="s">
+      <c r="B77" s="95" t="s">
         <v>73</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="92"/>
+      <c r="A78" s="99"/>
       <c r="B78" s="89"/>
       <c r="C78" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E78" s="31"/>
       <c r="F78" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="92"/>
+      <c r="A79" s="99"/>
       <c r="B79" s="90"/>
       <c r="E79" s="31"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="92"/>
-      <c r="B80" s="98" t="s">
+      <c r="A80" s="99"/>
+      <c r="B80" s="101" t="s">
         <v>4</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D80" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E80" s="39"/>
       <c r="F80" s="35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="92"/>
+      <c r="A81" s="99"/>
       <c r="B81" s="87"/>
       <c r="C81" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E81" s="42"/>
       <c r="F81" s="13" t="s">
@@ -4675,131 +4675,131 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="92"/>
+      <c r="A82" s="99"/>
       <c r="B82" s="87"/>
       <c r="C82" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E82" s="42"/>
       <c r="F82" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="92"/>
+      <c r="A83" s="99"/>
       <c r="B83" s="87"/>
       <c r="C83" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E83" s="31"/>
       <c r="F83" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="92"/>
+      <c r="A84" s="99"/>
       <c r="B84" s="87"/>
       <c r="C84" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D84" s="13" t="s">
         <v>156</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>157</v>
       </c>
       <c r="E84" s="34"/>
       <c r="F84" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="92"/>
+      <c r="A85" s="99"/>
       <c r="B85" s="87"/>
       <c r="C85" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D85" s="13" t="s">
         <v>162</v>
-      </c>
-      <c r="D85" s="13" t="s">
-        <v>163</v>
       </c>
       <c r="E85" s="31"/>
       <c r="F85" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="92"/>
+      <c r="A86" s="99"/>
       <c r="B86" s="87"/>
       <c r="C86" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D86" s="13" t="s">
         <v>198</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>200</v>
       </c>
       <c r="E86" s="31"/>
       <c r="F86" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="92"/>
+      <c r="A87" s="99"/>
       <c r="B87" s="87"/>
       <c r="C87" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E87" s="33"/>
       <c r="F87" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="92"/>
+      <c r="A88" s="99"/>
       <c r="B88" s="87"/>
       <c r="C88" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D88" s="13" t="s">
         <v>190</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>192</v>
       </c>
       <c r="E88" s="33"/>
       <c r="F88" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="92"/>
-      <c r="B89" s="101"/>
+      <c r="A89" s="99"/>
+      <c r="B89" s="102"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="92"/>
-      <c r="B90" s="98" t="s">
+      <c r="A90" s="99"/>
+      <c r="B90" s="101" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D90" s="35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E90" s="39"/>
       <c r="F90" s="35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="92"/>
+      <c r="A91" s="99"/>
       <c r="B91" s="87"/>
       <c r="C91" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E91" s="42"/>
       <c r="F91" s="13" t="s">
@@ -4807,155 +4807,155 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="92"/>
+      <c r="A92" s="99"/>
       <c r="B92" s="87"/>
       <c r="C92" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E92" s="42"/>
       <c r="F92" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="92"/>
+      <c r="A93" s="99"/>
       <c r="B93" s="87"/>
       <c r="C93" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D93" s="13" t="s">
         <v>142</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>143</v>
       </c>
       <c r="E93" s="42"/>
       <c r="F93" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="92"/>
+      <c r="A94" s="99"/>
       <c r="B94" s="87"/>
       <c r="C94" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E94" s="34"/>
       <c r="F94" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="92"/>
+      <c r="A95" s="99"/>
       <c r="B95" s="87"/>
       <c r="C95" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E95" s="43"/>
       <c r="F95" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="92"/>
+      <c r="A96" s="99"/>
       <c r="B96" s="87"/>
       <c r="C96" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E96" s="43"/>
       <c r="F96" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="92"/>
+      <c r="A97" s="99"/>
       <c r="B97" s="87"/>
       <c r="C97" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D97" s="13" t="s">
         <v>168</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>169</v>
       </c>
       <c r="E97" s="33"/>
       <c r="F97" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="92"/>
+      <c r="A98" s="99"/>
       <c r="B98" s="87"/>
       <c r="C98" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E98" s="33"/>
       <c r="F98" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="97"/>
-      <c r="B99" s="104"/>
+      <c r="A99" s="100"/>
+      <c r="B99" s="103"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="91" t="s">
+      <c r="A100" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="B100" s="93" t="s">
+      <c r="B100" s="95" t="s">
         <v>73</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D100" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E100" s="30"/>
       <c r="F100" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="92"/>
+      <c r="A101" s="99"/>
       <c r="B101" s="89"/>
       <c r="C101" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E101" s="33"/>
       <c r="F101" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="92"/>
+      <c r="A102" s="99"/>
       <c r="B102" s="89"/>
       <c r="C102" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E102" s="33"/>
       <c r="F102" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="92"/>
+      <c r="A103" s="99"/>
       <c r="B103" s="90"/>
       <c r="C103" s="36"/>
       <c r="D103" s="36"/>
@@ -4963,86 +4963,86 @@
       <c r="F103" s="36"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="92"/>
+      <c r="A104" s="99"/>
       <c r="B104" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="D104" s="13" t="s">
         <v>294</v>
-      </c>
-      <c r="C104" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>296</v>
       </c>
       <c r="E104" s="33"/>
       <c r="F104" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="92"/>
+      <c r="A105" s="99"/>
       <c r="B105" s="89"/>
       <c r="C105" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E105" s="33"/>
       <c r="F105" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="92"/>
+      <c r="A106" s="99"/>
       <c r="B106" s="89"/>
       <c r="C106" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E106" s="33"/>
       <c r="F106" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="92"/>
+      <c r="A107" s="99"/>
       <c r="B107" s="90"/>
       <c r="E107" s="33"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="92"/>
+      <c r="A108" s="99"/>
       <c r="B108" s="88" t="s">
         <v>79</v>
       </c>
       <c r="C108" s="35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D108" s="35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E108" s="39"/>
       <c r="F108" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="92"/>
-      <c r="B109" s="105"/>
+      <c r="A109" s="99"/>
+      <c r="B109" s="91"/>
       <c r="C109" s="70" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D109" s="70" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E109" s="71"/>
       <c r="F109" s="70" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="92"/>
+      <c r="A110" s="99"/>
       <c r="B110" s="90"/>
       <c r="C110" s="36"/>
       <c r="D110" s="36"/>
@@ -5050,114 +5050,114 @@
       <c r="F110" s="36"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="92"/>
-      <c r="B111" s="106" t="s">
-        <v>373</v>
+      <c r="A111" s="99"/>
+      <c r="B111" s="104" t="s">
+        <v>371</v>
       </c>
       <c r="C111" s="35" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D111" s="35" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E111" s="39"/>
       <c r="F111" s="35" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="99"/>
+      <c r="B112" s="105"/>
+      <c r="C112" s="70" t="s">
+        <v>376</v>
+      </c>
+      <c r="D112" s="70" t="s">
         <v>379</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="92"/>
-      <c r="B112" s="107"/>
-      <c r="C112" s="70" t="s">
-        <v>378</v>
-      </c>
-      <c r="D112" s="70" t="s">
-        <v>381</v>
       </c>
       <c r="E112" s="71"/>
       <c r="F112" s="70" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="92"/>
-      <c r="B113" s="108"/>
+      <c r="A113" s="99"/>
+      <c r="B113" s="106"/>
       <c r="C113" s="36"/>
       <c r="D113" s="36"/>
       <c r="E113" s="37"/>
       <c r="F113" s="36"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="92"/>
-      <c r="B114" s="102" t="s">
-        <v>333</v>
+      <c r="A114" s="99"/>
+      <c r="B114" s="96" t="s">
+        <v>331</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E114" s="33"/>
       <c r="F114" s="13" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="99"/>
+      <c r="B115" s="97"/>
+      <c r="C115" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="D115" s="13" t="s">
         <v>360</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="92"/>
-      <c r="B115" s="95"/>
-      <c r="C115" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>362</v>
       </c>
       <c r="E115" s="33"/>
       <c r="F115" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="97"/>
-      <c r="B116" s="103"/>
+      <c r="A116" s="100"/>
+      <c r="B116" s="98"/>
       <c r="C116" s="40"/>
       <c r="D116" s="40"/>
       <c r="E116" s="41"/>
       <c r="F116" s="40"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="91" t="s">
-        <v>164</v>
-      </c>
-      <c r="B117" s="93" t="s">
+      <c r="A117" s="93" t="s">
+        <v>163</v>
+      </c>
+      <c r="B117" s="95" t="s">
         <v>13</v>
       </c>
       <c r="C117" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D117" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E117" s="26"/>
       <c r="F117" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="110"/>
-      <c r="B118" s="105"/>
+      <c r="A118" s="94"/>
+      <c r="B118" s="91"/>
       <c r="C118" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D118" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="D118" s="13" t="s">
-        <v>176</v>
-      </c>
       <c r="F118" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="110"/>
+      <c r="A119" s="94"/>
       <c r="B119" s="90"/>
       <c r="C119" s="36"/>
       <c r="D119" s="36"/>
@@ -5165,282 +5165,282 @@
       <c r="F119" s="36"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="110"/>
+      <c r="A120" s="94"/>
       <c r="B120" s="88" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F120" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="110"/>
-      <c r="B121" s="105"/>
+      <c r="A121" s="94"/>
+      <c r="B121" s="91"/>
       <c r="C121" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F121" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="94"/>
+      <c r="B122" s="91"/>
+      <c r="C122" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F122" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="94"/>
+      <c r="B123" s="91"/>
+      <c r="C123" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="F123" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="94"/>
+      <c r="B124" s="91"/>
+      <c r="C124" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="D121" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="F121" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="110"/>
-      <c r="B122" s="105"/>
-      <c r="C122" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="D122" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F122" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="110"/>
-      <c r="B123" s="105"/>
-      <c r="C123" s="13" t="s">
+      <c r="D124" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="D123" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F123" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="110"/>
-      <c r="B124" s="105"/>
-      <c r="C124" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>181</v>
-      </c>
       <c r="F124" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="110"/>
-      <c r="B125" s="105"/>
+      <c r="A125" s="94"/>
+      <c r="B125" s="91"/>
       <c r="C125" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F125" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="110"/>
+      <c r="A126" s="94"/>
       <c r="B126" s="90"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="110"/>
+      <c r="A127" s="94"/>
       <c r="B127" s="88" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C127" s="35" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D127" s="35" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E127" s="35"/>
       <c r="F127" s="35" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="94"/>
+      <c r="B128" s="91"/>
+      <c r="C128" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D128" s="13" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="110"/>
-      <c r="B128" s="105"/>
-      <c r="C128" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="D128" s="13" t="s">
-        <v>212</v>
-      </c>
       <c r="F128" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="110"/>
-      <c r="B129" s="105"/>
+      <c r="A129" s="94"/>
+      <c r="B129" s="91"/>
       <c r="C129" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F129" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="110"/>
-      <c r="B130" s="105"/>
+      <c r="A130" s="94"/>
+      <c r="B130" s="91"/>
       <c r="C130" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F130" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="110"/>
-      <c r="B131" s="105"/>
+      <c r="A131" s="94"/>
+      <c r="B131" s="91"/>
       <c r="C131" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F131" s="13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="110"/>
-      <c r="B132" s="105"/>
+      <c r="A132" s="94"/>
+      <c r="B132" s="91"/>
       <c r="C132" s="44" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D132" s="44" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E132" s="44"/>
       <c r="F132" s="13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="110"/>
-      <c r="B133" s="105"/>
+      <c r="A133" s="94"/>
+      <c r="B133" s="91"/>
       <c r="C133" s="44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D133" s="44" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E133" s="44"/>
       <c r="F133" s="13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="110"/>
-      <c r="B134" s="105"/>
+      <c r="A134" s="94"/>
+      <c r="B134" s="91"/>
       <c r="C134" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D134" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="F134" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="F134" s="13" t="s">
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="94"/>
+      <c r="B135" s="91"/>
+      <c r="C135" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="F135" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="94"/>
+      <c r="B136" s="91"/>
+      <c r="C136" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D136" s="13" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="110"/>
-      <c r="B135" s="105"/>
-      <c r="C135" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="F135" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="110"/>
-      <c r="B136" s="105"/>
-      <c r="C136" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>222</v>
-      </c>
       <c r="F136" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="110"/>
-      <c r="B137" s="105"/>
+      <c r="A137" s="94"/>
+      <c r="B137" s="91"/>
       <c r="C137" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D137" s="44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E137" s="44"/>
       <c r="F137" s="44" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="110"/>
-      <c r="B138" s="105"/>
+      <c r="A138" s="94"/>
+      <c r="B138" s="91"/>
       <c r="C138" s="44" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D138" s="44" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E138" s="44"/>
       <c r="F138" s="44" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="110"/>
-      <c r="B139" s="105"/>
+      <c r="A139" s="94"/>
+      <c r="B139" s="91"/>
       <c r="C139" s="44" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D139" s="44" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E139" s="44"/>
       <c r="F139" s="44" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="110"/>
-      <c r="B140" s="105"/>
+      <c r="A140" s="94"/>
+      <c r="B140" s="91"/>
       <c r="C140" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D140" s="44" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E140" s="44"/>
       <c r="F140" s="44" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="110"/>
+      <c r="A141" s="94"/>
       <c r="B141" s="90"/>
       <c r="C141" s="44"/>
       <c r="D141" s="44"/>
@@ -5448,79 +5448,79 @@
       <c r="F141" s="44"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="110"/>
+      <c r="A142" s="94"/>
       <c r="B142" s="88" t="s">
+        <v>222</v>
+      </c>
+      <c r="C142" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="C142" s="35" t="s">
-        <v>226</v>
-      </c>
       <c r="D142" s="35" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E142" s="35"/>
       <c r="F142" s="35" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="110"/>
-      <c r="B143" s="105"/>
+      <c r="A143" s="94"/>
+      <c r="B143" s="91"/>
       <c r="C143" s="70" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D143" s="70" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E143" s="70"/>
       <c r="F143" s="70" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="110"/>
-      <c r="B144" s="105"/>
+      <c r="A144" s="94"/>
+      <c r="B144" s="91"/>
       <c r="C144" s="70" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D144" s="70" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E144" s="70"/>
       <c r="F144" s="70" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="110"/>
-      <c r="B145" s="105"/>
+      <c r="A145" s="94"/>
+      <c r="B145" s="91"/>
       <c r="C145" s="72" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D145" s="72" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E145" s="72"/>
       <c r="F145" s="72" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="110"/>
-      <c r="B146" s="105"/>
+      <c r="A146" s="94"/>
+      <c r="B146" s="91"/>
       <c r="C146" s="72" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D146" s="72" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E146" s="72"/>
       <c r="F146" s="72" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="110"/>
+      <c r="A147" s="94"/>
       <c r="B147" s="90"/>
       <c r="C147" s="36"/>
       <c r="D147" s="36"/>
@@ -5528,33 +5528,33 @@
       <c r="F147" s="36"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="110"/>
-      <c r="B148" s="109" t="s">
-        <v>388</v>
+      <c r="A148" s="94"/>
+      <c r="B148" s="92" t="s">
+        <v>386</v>
       </c>
       <c r="C148" s="70" t="s">
+        <v>387</v>
+      </c>
+      <c r="D148" s="70" t="s">
         <v>389</v>
-      </c>
-      <c r="D148" s="70" t="s">
-        <v>391</v>
       </c>
       <c r="E148" s="70"/>
       <c r="F148" s="70" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="110"/>
-      <c r="B149" s="109"/>
+      <c r="A149" s="94"/>
+      <c r="B149" s="92"/>
       <c r="C149" s="70" t="s">
+        <v>388</v>
+      </c>
+      <c r="D149" s="70" t="s">
         <v>390</v>
-      </c>
-      <c r="D149" s="70" t="s">
-        <v>392</v>
       </c>
       <c r="E149" s="70"/>
       <c r="F149" s="70" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -5565,12 +5565,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A117:A149"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="A2:A44"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="B34:B44"/>
+    <mergeCell ref="A45:A76"/>
+    <mergeCell ref="B65:B76"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B45:B54"/>
+    <mergeCell ref="B55:B64"/>
     <mergeCell ref="B114:B116"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A77:A99"/>
@@ -5581,15 +5584,12 @@
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="B34:B44"/>
-    <mergeCell ref="A45:A76"/>
-    <mergeCell ref="B65:B76"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B45:B54"/>
-    <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A117:A149"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="B120:B126"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5606,47 +5606,47 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="49" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="49" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="52" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="49" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="49" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="49" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="49" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="50" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="51" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">

--- a/Fischer_Tropsch/FischerTropsch_Naphta_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Naphta_Greenfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Greenfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8CDC9E-9129-46F1-B107-93D0C9AE9AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215824B0-835F-40C1-8D67-D6671FAC6B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1381,10 +1381,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1593,21 +1593,21 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1615,10 +1615,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1630,27 +1630,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1660,26 +1660,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1734,32 +1730,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1767,8 +1754,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1776,23 +1772,14 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2327,10 +2314,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="79" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2347,8 +2334,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="74"/>
-      <c r="B3" s="81"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="77"/>
       <c r="C3" t="s">
         <v>84</v>
       </c>
@@ -2363,8 +2350,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="74"/>
-      <c r="B4" s="81"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="77"/>
       <c r="C4" t="s">
         <v>10</v>
       </c>
@@ -2372,15 +2359,15 @@
         <v>26</v>
       </c>
       <c r="E4" s="20">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="74"/>
-      <c r="B5" s="81"/>
+      <c r="A5" s="70"/>
+      <c r="B5" s="77"/>
       <c r="C5" t="s">
         <v>11</v>
       </c>
@@ -2395,8 +2382,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="74"/>
-      <c r="B6" s="81"/>
+      <c r="A6" s="70"/>
+      <c r="B6" s="77"/>
       <c r="C6" t="s">
         <v>13</v>
       </c>
@@ -2411,8 +2398,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="74"/>
-      <c r="B7" s="81"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="77"/>
       <c r="C7" t="s">
         <v>15</v>
       </c>
@@ -2427,8 +2414,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="74"/>
-      <c r="B8" s="84" t="s">
+      <c r="A8" s="70"/>
+      <c r="B8" s="80" t="s">
         <v>330</v>
       </c>
       <c r="C8" s="35" t="s">
@@ -2445,8 +2432,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="74"/>
-      <c r="B9" s="85"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="13" t="s">
         <v>85</v>
       </c>
@@ -2461,8 +2448,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="74"/>
-      <c r="B10" s="85"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="81"/>
       <c r="C10" s="13" t="s">
         <v>10</v>
       </c>
@@ -2477,8 +2464,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="74"/>
-      <c r="B11" s="85"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="81"/>
       <c r="C11" s="13" t="s">
         <v>11</v>
       </c>
@@ -2493,8 +2480,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="74"/>
-      <c r="B12" s="85"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="81"/>
       <c r="C12" s="13" t="s">
         <v>86</v>
       </c>
@@ -2509,8 +2496,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="74"/>
-      <c r="B13" s="85"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="13" t="s">
         <v>237</v>
       </c>
@@ -2525,8 +2512,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="74"/>
-      <c r="B14" s="85"/>
+      <c r="A14" s="70"/>
+      <c r="B14" s="81"/>
       <c r="C14" s="13" t="s">
         <v>368</v>
       </c>
@@ -2541,8 +2528,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="74"/>
-      <c r="B15" s="85"/>
+      <c r="A15" s="70"/>
+      <c r="B15" s="81"/>
       <c r="C15" s="13" t="s">
         <v>13</v>
       </c>
@@ -2557,8 +2544,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="74"/>
-      <c r="B16" s="86"/>
+      <c r="A16" s="70"/>
+      <c r="B16" s="82"/>
       <c r="C16" s="36" t="s">
         <v>15</v>
       </c>
@@ -2573,8 +2560,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="74"/>
-      <c r="B17" s="88" t="s">
+      <c r="A17" s="70"/>
+      <c r="B17" s="84" t="s">
         <v>262</v>
       </c>
       <c r="C17" s="35" t="s">
@@ -2591,8 +2578,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="74"/>
-      <c r="B18" s="89"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="85"/>
       <c r="C18" s="13" t="s">
         <v>84</v>
       </c>
@@ -2607,8 +2594,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="74"/>
-      <c r="B19" s="89"/>
+      <c r="A19" s="70"/>
+      <c r="B19" s="85"/>
       <c r="C19" s="13" t="s">
         <v>10</v>
       </c>
@@ -2623,8 +2610,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="74"/>
-      <c r="B20" s="89"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="85"/>
       <c r="C20" s="13" t="s">
         <v>11</v>
       </c>
@@ -2639,8 +2626,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="74"/>
-      <c r="B21" s="89"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="85"/>
       <c r="C21" s="13" t="s">
         <v>13</v>
       </c>
@@ -2655,8 +2642,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="74"/>
-      <c r="B22" s="90"/>
+      <c r="A22" s="70"/>
+      <c r="B22" s="86"/>
       <c r="C22" s="36" t="s">
         <v>15</v>
       </c>
@@ -2671,8 +2658,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="74"/>
-      <c r="B23" s="87" t="s">
+      <c r="A23" s="70"/>
+      <c r="B23" s="83" t="s">
         <v>229</v>
       </c>
       <c r="C23" s="44" t="s">
@@ -2689,8 +2676,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="74"/>
-      <c r="B24" s="87"/>
+      <c r="A24" s="70"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="44" t="s">
         <v>270</v>
       </c>
@@ -2705,8 +2692,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="74"/>
-      <c r="B25" s="87"/>
+      <c r="A25" s="70"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="44" t="s">
         <v>10</v>
       </c>
@@ -2721,8 +2708,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="74"/>
-      <c r="B26" s="87"/>
+      <c r="A26" s="70"/>
+      <c r="B26" s="83"/>
       <c r="C26" s="44" t="s">
         <v>11</v>
       </c>
@@ -2737,8 +2724,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="74"/>
-      <c r="B27" s="87"/>
+      <c r="A27" s="70"/>
+      <c r="B27" s="83"/>
       <c r="C27" s="44" t="s">
         <v>13</v>
       </c>
@@ -2753,8 +2740,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="74"/>
-      <c r="B28" s="87"/>
+      <c r="A28" s="70"/>
+      <c r="B28" s="83"/>
       <c r="C28" s="44" t="s">
         <v>15</v>
       </c>
@@ -2769,10 +2756,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="73" t="s">
+      <c r="A29" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="76" t="s">
+      <c r="B29" s="72" t="s">
         <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2789,8 +2776,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="74"/>
-      <c r="B30" s="77"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="73"/>
       <c r="C30" t="s">
         <v>11</v>
       </c>
@@ -2805,8 +2792,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="74"/>
-      <c r="B31" s="77"/>
+      <c r="A31" s="70"/>
+      <c r="B31" s="73"/>
       <c r="C31" t="s">
         <v>13</v>
       </c>
@@ -2821,8 +2808,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="74"/>
-      <c r="B32" s="77"/>
+      <c r="A32" s="70"/>
+      <c r="B32" s="73"/>
       <c r="C32" t="s">
         <v>20</v>
       </c>
@@ -2837,8 +2824,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="74"/>
-      <c r="B33" s="77"/>
+      <c r="A33" s="70"/>
+      <c r="B33" s="73"/>
       <c r="C33" t="s">
         <v>35</v>
       </c>
@@ -2853,8 +2840,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="74"/>
-      <c r="B34" s="77"/>
+      <c r="A34" s="70"/>
+      <c r="B34" s="73"/>
       <c r="C34" t="s">
         <v>36</v>
       </c>
@@ -2869,8 +2856,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="74"/>
-      <c r="B35" s="77"/>
+      <c r="A35" s="70"/>
+      <c r="B35" s="73"/>
       <c r="C35" t="s">
         <v>15</v>
       </c>
@@ -2885,8 +2872,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="74"/>
-      <c r="B36" s="78"/>
+      <c r="A36" s="70"/>
+      <c r="B36" s="74"/>
       <c r="C36" s="5" t="s">
         <v>88</v>
       </c>
@@ -2901,8 +2888,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="74"/>
-      <c r="B37" s="79" t="s">
+      <c r="A37" s="70"/>
+      <c r="B37" s="75" t="s">
         <v>305</v>
       </c>
       <c r="C37" s="26" t="s">
@@ -2919,8 +2906,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="74"/>
-      <c r="B38" s="77"/>
+      <c r="A38" s="70"/>
+      <c r="B38" s="73"/>
       <c r="C38" s="13" t="s">
         <v>11</v>
       </c>
@@ -2935,8 +2922,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="74"/>
-      <c r="B39" s="77"/>
+      <c r="A39" s="70"/>
+      <c r="B39" s="73"/>
       <c r="C39" s="13" t="s">
         <v>13</v>
       </c>
@@ -2951,8 +2938,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="74"/>
-      <c r="B40" s="77"/>
+      <c r="A40" s="70"/>
+      <c r="B40" s="73"/>
       <c r="C40" s="13" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +2954,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="74"/>
-      <c r="B41" s="77"/>
+      <c r="A41" s="70"/>
+      <c r="B41" s="73"/>
       <c r="C41" s="13" t="s">
         <v>35</v>
       </c>
@@ -2983,8 +2970,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="74"/>
-      <c r="B42" s="77"/>
+      <c r="A42" s="70"/>
+      <c r="B42" s="73"/>
       <c r="C42" s="13" t="s">
         <v>36</v>
       </c>
@@ -2999,8 +2986,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="74"/>
-      <c r="B43" s="77"/>
+      <c r="A43" s="70"/>
+      <c r="B43" s="73"/>
       <c r="C43" s="13" t="s">
         <v>15</v>
       </c>
@@ -3015,8 +3002,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="74"/>
-      <c r="B44" s="77"/>
+      <c r="A44" s="70"/>
+      <c r="B44" s="73"/>
       <c r="C44" s="36" t="s">
         <v>88</v>
       </c>
@@ -3031,8 +3018,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="74"/>
-      <c r="B45" s="79" t="s">
+      <c r="A45" s="70"/>
+      <c r="B45" s="75" t="s">
         <v>201</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -3049,8 +3036,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="74"/>
-      <c r="B46" s="81"/>
+      <c r="A46" s="70"/>
+      <c r="B46" s="77"/>
       <c r="C46" t="s">
         <v>21</v>
       </c>
@@ -3066,8 +3053,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="74"/>
-      <c r="B47" s="81"/>
+      <c r="A47" s="70"/>
+      <c r="B47" s="77"/>
       <c r="C47" t="s">
         <v>16</v>
       </c>
@@ -3082,8 +3069,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="74"/>
-      <c r="B48" s="81"/>
+      <c r="A48" s="70"/>
+      <c r="B48" s="77"/>
       <c r="C48" t="s">
         <v>17</v>
       </c>
@@ -3098,8 +3085,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="74"/>
-      <c r="B49" s="81"/>
+      <c r="A49" s="70"/>
+      <c r="B49" s="77"/>
       <c r="C49" t="s">
         <v>35</v>
       </c>
@@ -3114,8 +3101,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="74"/>
-      <c r="B50" s="81"/>
+      <c r="A50" s="70"/>
+      <c r="B50" s="77"/>
       <c r="C50" t="s">
         <v>36</v>
       </c>
@@ -3130,8 +3117,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="74"/>
-      <c r="B51" s="81"/>
+      <c r="A51" s="70"/>
+      <c r="B51" s="77"/>
       <c r="C51" t="s">
         <v>89</v>
       </c>
@@ -3146,8 +3133,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="74"/>
-      <c r="B52" s="81"/>
+      <c r="A52" s="70"/>
+      <c r="B52" s="77"/>
       <c r="C52" t="s">
         <v>88</v>
       </c>
@@ -3162,8 +3149,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="74"/>
-      <c r="B53" s="81"/>
+      <c r="A53" s="70"/>
+      <c r="B53" s="77"/>
       <c r="C53" t="s">
         <v>13</v>
       </c>
@@ -3178,8 +3165,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="75"/>
-      <c r="B54" s="82"/>
+      <c r="A54" s="71"/>
+      <c r="B54" s="78"/>
       <c r="C54" s="15" t="s">
         <v>15</v>
       </c>
@@ -3194,7 +3181,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="73" t="s">
+      <c r="A55" s="69" t="s">
         <v>72</v>
       </c>
       <c r="B55" s="11" t="s">
@@ -3214,8 +3201,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="74"/>
-      <c r="B56" s="79" t="s">
+      <c r="A56" s="70"/>
+      <c r="B56" s="75" t="s">
         <v>4</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -3232,8 +3219,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="74"/>
-      <c r="B57" s="77"/>
+      <c r="A57" s="70"/>
+      <c r="B57" s="73"/>
       <c r="C57" t="s">
         <v>10</v>
       </c>
@@ -3248,8 +3235,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="74"/>
-      <c r="B58" s="77"/>
+      <c r="A58" s="70"/>
+      <c r="B58" s="73"/>
       <c r="C58" t="s">
         <v>17</v>
       </c>
@@ -3264,8 +3251,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="74"/>
-      <c r="B59" s="77"/>
+      <c r="A59" s="70"/>
+      <c r="B59" s="73"/>
       <c r="C59" t="s">
         <v>18</v>
       </c>
@@ -3280,8 +3267,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="74"/>
-      <c r="B60" s="77"/>
+      <c r="A60" s="70"/>
+      <c r="B60" s="73"/>
       <c r="C60" t="s">
         <v>13</v>
       </c>
@@ -3296,8 +3283,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="74"/>
-      <c r="B61" s="77"/>
+      <c r="A61" s="70"/>
+      <c r="B61" s="73"/>
       <c r="C61" t="s">
         <v>68</v>
       </c>
@@ -3312,8 +3299,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="74"/>
-      <c r="B62" s="78"/>
+      <c r="A62" s="70"/>
+      <c r="B62" s="74"/>
       <c r="C62" s="5" t="s">
         <v>15</v>
       </c>
@@ -3328,8 +3315,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="74"/>
-      <c r="B63" s="79" t="s">
+      <c r="A63" s="70"/>
+      <c r="B63" s="75" t="s">
         <v>5</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -3346,8 +3333,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="74"/>
-      <c r="B64" s="77"/>
+      <c r="A64" s="70"/>
+      <c r="B64" s="73"/>
       <c r="C64" t="s">
         <v>10</v>
       </c>
@@ -3362,8 +3349,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="74"/>
-      <c r="B65" s="77"/>
+      <c r="A65" s="70"/>
+      <c r="B65" s="73"/>
       <c r="C65" t="s">
         <v>17</v>
       </c>
@@ -3378,8 +3365,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="74"/>
-      <c r="B66" s="77"/>
+      <c r="A66" s="70"/>
+      <c r="B66" s="73"/>
       <c r="C66" t="s">
         <v>18</v>
       </c>
@@ -3394,8 +3381,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="74"/>
-      <c r="B67" s="77"/>
+      <c r="A67" s="70"/>
+      <c r="B67" s="73"/>
       <c r="C67" t="s">
         <v>13</v>
       </c>
@@ -3410,8 +3397,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="74"/>
-      <c r="B68" s="77"/>
+      <c r="A68" s="70"/>
+      <c r="B68" s="73"/>
       <c r="C68" t="s">
         <v>68</v>
       </c>
@@ -3426,8 +3413,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="75"/>
-      <c r="B69" s="80"/>
+      <c r="A69" s="71"/>
+      <c r="B69" s="76"/>
       <c r="C69" s="15" t="s">
         <v>15</v>
       </c>
@@ -3442,7 +3429,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="73" t="s">
+      <c r="A70" s="69" t="s">
         <v>76</v>
       </c>
       <c r="B70" s="56" t="s">
@@ -3462,7 +3449,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="74"/>
+      <c r="A71" s="70"/>
       <c r="B71" s="6" t="s">
         <v>288</v>
       </c>
@@ -3480,7 +3467,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="74"/>
+      <c r="A72" s="70"/>
       <c r="B72" s="17" t="s">
         <v>79</v>
       </c>
@@ -3498,14 +3485,14 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="74"/>
+      <c r="A73" s="70"/>
       <c r="B73" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="69" t="s">
+      <c r="C73" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="D73" s="69" t="s">
+      <c r="D73" s="18" t="s">
         <v>373</v>
       </c>
       <c r="E73" s="19">
@@ -3516,7 +3503,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="75"/>
+      <c r="A74" s="71"/>
       <c r="B74" s="61" t="s">
         <v>331</v>
       </c>
@@ -3558,7 +3545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
@@ -3591,10 +3578,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="89" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3609,8 +3596,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="99"/>
-      <c r="B3" s="89"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="85"/>
       <c r="C3" s="13" t="s">
         <v>107</v>
       </c>
@@ -3623,8 +3610,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="89"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
       </c>
@@ -3637,8 +3624,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="99"/>
-      <c r="B5" s="89"/>
+      <c r="A5" s="88"/>
+      <c r="B5" s="85"/>
       <c r="C5" s="13" t="s">
         <v>138</v>
       </c>
@@ -3651,8 +3638,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="99"/>
-      <c r="B6" s="89"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="85"/>
       <c r="C6" s="13" t="s">
         <v>141</v>
       </c>
@@ -3665,8 +3652,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="99"/>
-      <c r="B7" s="89"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="85"/>
       <c r="C7" s="13" t="s">
         <v>155</v>
       </c>
@@ -3679,8 +3666,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="99"/>
-      <c r="B8" s="89"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="85"/>
       <c r="C8" s="13" t="s">
         <v>196</v>
       </c>
@@ -3693,8 +3680,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="99"/>
-      <c r="B9" s="89"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="85"/>
       <c r="C9" s="13" t="s">
         <v>167</v>
       </c>
@@ -3707,8 +3694,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="99"/>
-      <c r="B10" s="89"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="85"/>
       <c r="C10" s="13" t="s">
         <v>188</v>
       </c>
@@ -3721,13 +3708,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="99"/>
-      <c r="B11" s="89"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="85"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="99"/>
-      <c r="B12" s="107" t="s">
+      <c r="A12" s="88"/>
+      <c r="B12" s="90" t="s">
         <v>364</v>
       </c>
       <c r="C12" s="35" t="s">
@@ -3742,8 +3729,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="99"/>
-      <c r="B13" s="97"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="91"/>
       <c r="C13" s="13" t="s">
         <v>363</v>
       </c>
@@ -3756,8 +3743,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="99"/>
-      <c r="B14" s="97"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="91"/>
       <c r="C14" s="13" t="s">
         <v>380</v>
       </c>
@@ -3770,8 +3757,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
-      <c r="B15" s="97"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="91"/>
       <c r="C15" s="13" t="s">
         <v>139</v>
       </c>
@@ -3784,8 +3771,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="99"/>
-      <c r="B16" s="97"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="91"/>
       <c r="C16" s="13" t="s">
         <v>238</v>
       </c>
@@ -3798,8 +3785,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="99"/>
-      <c r="B17" s="97"/>
+      <c r="A17" s="88"/>
+      <c r="B17" s="91"/>
       <c r="C17" s="13" t="s">
         <v>84</v>
       </c>
@@ -3812,8 +3799,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="99"/>
-      <c r="B18" s="97"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="91"/>
       <c r="C18" s="13" t="s">
         <v>141</v>
       </c>
@@ -3826,8 +3813,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="99"/>
-      <c r="B19" s="97"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="13" t="s">
         <v>155</v>
       </c>
@@ -3840,8 +3827,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="99"/>
-      <c r="B20" s="97"/>
+      <c r="A20" s="88"/>
+      <c r="B20" s="91"/>
       <c r="C20" s="13" t="s">
         <v>196</v>
       </c>
@@ -3854,8 +3841,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="99"/>
-      <c r="B21" s="97"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="91"/>
       <c r="C21" s="13" t="s">
         <v>167</v>
       </c>
@@ -3868,8 +3855,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="99"/>
-      <c r="B22" s="97"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="91"/>
       <c r="C22" s="13" t="s">
         <v>188</v>
       </c>
@@ -3882,16 +3869,16 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="99"/>
-      <c r="B23" s="108"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
       <c r="F23" s="36"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="99"/>
-      <c r="B24" s="88" t="s">
+      <c r="A24" s="88"/>
+      <c r="B24" s="84" t="s">
         <v>262</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -3906,8 +3893,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="99"/>
-      <c r="B25" s="89"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="13" t="s">
         <v>107</v>
       </c>
@@ -3920,8 +3907,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="99"/>
-      <c r="B26" s="89"/>
+      <c r="A26" s="88"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="13" t="s">
         <v>84</v>
       </c>
@@ -3934,8 +3921,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="99"/>
-      <c r="B27" s="89"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="85"/>
       <c r="C27" s="13" t="s">
         <v>283</v>
       </c>
@@ -3948,8 +3935,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="99"/>
-      <c r="B28" s="89"/>
+      <c r="A28" s="88"/>
+      <c r="B28" s="85"/>
       <c r="C28" s="13" t="s">
         <v>141</v>
       </c>
@@ -3962,8 +3949,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="99"/>
-      <c r="B29" s="89"/>
+      <c r="A29" s="88"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="13" t="s">
         <v>155</v>
       </c>
@@ -3976,8 +3963,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="99"/>
-      <c r="B30" s="89"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="85"/>
       <c r="C30" s="13" t="s">
         <v>196</v>
       </c>
@@ -3990,8 +3977,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="99"/>
-      <c r="B31" s="89"/>
+      <c r="A31" s="88"/>
+      <c r="B31" s="85"/>
       <c r="C31" s="13" t="s">
         <v>167</v>
       </c>
@@ -4004,8 +3991,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="99"/>
-      <c r="B32" s="89"/>
+      <c r="A32" s="88"/>
+      <c r="B32" s="85"/>
       <c r="C32" s="13" t="s">
         <v>188</v>
       </c>
@@ -4018,16 +4005,16 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="99"/>
-      <c r="B33" s="90"/>
+      <c r="A33" s="88"/>
+      <c r="B33" s="86"/>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
       <c r="E33" s="37"/>
       <c r="F33" s="36"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="99"/>
-      <c r="B34" s="87" t="s">
+      <c r="A34" s="88"/>
+      <c r="B34" s="83" t="s">
         <v>229</v>
       </c>
       <c r="C34" s="13" t="s">
@@ -4042,8 +4029,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="99"/>
-      <c r="B35" s="87"/>
+      <c r="A35" s="88"/>
+      <c r="B35" s="83"/>
       <c r="C35" s="13" t="s">
         <v>107</v>
       </c>
@@ -4056,8 +4043,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="99"/>
-      <c r="B36" s="87"/>
+      <c r="A36" s="88"/>
+      <c r="B36" s="83"/>
       <c r="C36" s="13" t="s">
         <v>84</v>
       </c>
@@ -4070,8 +4057,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="99"/>
-      <c r="B37" s="87"/>
+      <c r="A37" s="88"/>
+      <c r="B37" s="83"/>
       <c r="C37" s="13" t="s">
         <v>270</v>
       </c>
@@ -4084,8 +4071,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="99"/>
-      <c r="B38" s="87"/>
+      <c r="A38" s="88"/>
+      <c r="B38" s="83"/>
       <c r="C38" s="13" t="s">
         <v>248</v>
       </c>
@@ -4098,8 +4085,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="99"/>
-      <c r="B39" s="87"/>
+      <c r="A39" s="88"/>
+      <c r="B39" s="83"/>
       <c r="C39" s="13" t="s">
         <v>141</v>
       </c>
@@ -4112,8 +4099,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="99"/>
-      <c r="B40" s="87"/>
+      <c r="A40" s="88"/>
+      <c r="B40" s="83"/>
       <c r="C40" s="13" t="s">
         <v>155</v>
       </c>
@@ -4126,8 +4113,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="99"/>
-      <c r="B41" s="87"/>
+      <c r="A41" s="88"/>
+      <c r="B41" s="83"/>
       <c r="C41" s="13" t="s">
         <v>196</v>
       </c>
@@ -4140,8 +4127,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="99"/>
-      <c r="B42" s="87"/>
+      <c r="A42" s="88"/>
+      <c r="B42" s="83"/>
       <c r="C42" s="13" t="s">
         <v>167</v>
       </c>
@@ -4154,8 +4141,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="99"/>
-      <c r="B43" s="87"/>
+      <c r="A43" s="88"/>
+      <c r="B43" s="83"/>
       <c r="C43" s="13" t="s">
         <v>188</v>
       </c>
@@ -4168,15 +4155,15 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="99"/>
-      <c r="B44" s="87"/>
+      <c r="A44" s="88"/>
+      <c r="B44" s="83"/>
       <c r="E44" s="33"/>
     </row>
     <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="93" t="s">
+      <c r="A45" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="110" t="s">
+      <c r="B45" s="96" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="26" t="s">
@@ -4191,8 +4178,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="99"/>
-      <c r="B46" s="87"/>
+      <c r="A46" s="88"/>
+      <c r="B46" s="83"/>
       <c r="C46" s="13" t="s">
         <v>111</v>
       </c>
@@ -4205,8 +4192,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="99"/>
-      <c r="B47" s="87"/>
+      <c r="A47" s="88"/>
+      <c r="B47" s="83"/>
       <c r="C47" s="13" t="s">
         <v>135</v>
       </c>
@@ -4219,8 +4206,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="99"/>
-      <c r="B48" s="87"/>
+      <c r="A48" s="88"/>
+      <c r="B48" s="83"/>
       <c r="C48" s="13" t="s">
         <v>136</v>
       </c>
@@ -4233,8 +4220,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="99"/>
-      <c r="B49" s="87"/>
+      <c r="A49" s="88"/>
+      <c r="B49" s="83"/>
       <c r="C49" s="13" t="s">
         <v>141</v>
       </c>
@@ -4247,8 +4234,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="99"/>
-      <c r="B50" s="87"/>
+      <c r="A50" s="88"/>
+      <c r="B50" s="83"/>
       <c r="C50" s="13" t="s">
         <v>155</v>
       </c>
@@ -4261,8 +4248,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="99"/>
-      <c r="B51" s="87"/>
+      <c r="A51" s="88"/>
+      <c r="B51" s="83"/>
       <c r="C51" s="13" t="s">
         <v>196</v>
       </c>
@@ -4275,8 +4262,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="99"/>
-      <c r="B52" s="87"/>
+      <c r="A52" s="88"/>
+      <c r="B52" s="83"/>
       <c r="C52" s="13" t="s">
         <v>167</v>
       </c>
@@ -4289,8 +4276,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="99"/>
-      <c r="B53" s="87"/>
+      <c r="A53" s="88"/>
+      <c r="B53" s="83"/>
       <c r="C53" s="13" t="s">
         <v>188</v>
       </c>
@@ -4303,16 +4290,16 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="99"/>
-      <c r="B54" s="102"/>
+      <c r="A54" s="88"/>
+      <c r="B54" s="97"/>
       <c r="C54" s="36"/>
       <c r="D54" s="36"/>
       <c r="E54" s="37"/>
       <c r="F54" s="36"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="99"/>
-      <c r="B55" s="87" t="s">
+      <c r="A55" s="88"/>
+      <c r="B55" s="83" t="s">
         <v>305</v>
       </c>
       <c r="C55" s="13" t="s">
@@ -4327,8 +4314,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="99"/>
-      <c r="B56" s="87"/>
+      <c r="A56" s="88"/>
+      <c r="B56" s="83"/>
       <c r="C56" s="13" t="s">
         <v>111</v>
       </c>
@@ -4341,8 +4328,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="99"/>
-      <c r="B57" s="87"/>
+      <c r="A57" s="88"/>
+      <c r="B57" s="83"/>
       <c r="C57" s="13" t="s">
         <v>135</v>
       </c>
@@ -4355,8 +4342,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="99"/>
-      <c r="B58" s="87"/>
+      <c r="A58" s="88"/>
+      <c r="B58" s="83"/>
       <c r="C58" s="13" t="s">
         <v>136</v>
       </c>
@@ -4369,8 +4356,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="99"/>
-      <c r="B59" s="87"/>
+      <c r="A59" s="88"/>
+      <c r="B59" s="83"/>
       <c r="C59" s="13" t="s">
         <v>141</v>
       </c>
@@ -4383,8 +4370,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="99"/>
-      <c r="B60" s="87"/>
+      <c r="A60" s="88"/>
+      <c r="B60" s="83"/>
       <c r="C60" s="13" t="s">
         <v>155</v>
       </c>
@@ -4397,8 +4384,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="99"/>
-      <c r="B61" s="87"/>
+      <c r="A61" s="88"/>
+      <c r="B61" s="83"/>
       <c r="C61" s="13" t="s">
         <v>196</v>
       </c>
@@ -4411,8 +4398,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="99"/>
-      <c r="B62" s="87"/>
+      <c r="A62" s="88"/>
+      <c r="B62" s="83"/>
       <c r="C62" s="13" t="s">
         <v>167</v>
       </c>
@@ -4425,8 +4412,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="99"/>
-      <c r="B63" s="87"/>
+      <c r="A63" s="88"/>
+      <c r="B63" s="83"/>
       <c r="C63" s="13" t="s">
         <v>188</v>
       </c>
@@ -4439,13 +4426,13 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="99"/>
-      <c r="B64" s="102"/>
+      <c r="A64" s="88"/>
+      <c r="B64" s="97"/>
       <c r="E64" s="33"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="99"/>
-      <c r="B65" s="101" t="s">
+      <c r="A65" s="88"/>
+      <c r="B65" s="94" t="s">
         <v>6</v>
       </c>
       <c r="C65" s="35" t="s">
@@ -4460,8 +4447,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="99"/>
-      <c r="B66" s="87"/>
+      <c r="A66" s="88"/>
+      <c r="B66" s="83"/>
       <c r="C66" s="13" t="s">
         <v>113</v>
       </c>
@@ -4474,8 +4461,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="99"/>
-      <c r="B67" s="89"/>
+      <c r="A67" s="88"/>
+      <c r="B67" s="85"/>
       <c r="C67" s="13" t="s">
         <v>111</v>
       </c>
@@ -4488,8 +4475,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="99"/>
-      <c r="B68" s="89"/>
+      <c r="A68" s="88"/>
+      <c r="B68" s="85"/>
       <c r="C68" s="13" t="s">
         <v>107</v>
       </c>
@@ -4502,8 +4489,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="99"/>
-      <c r="B69" s="89"/>
+      <c r="A69" s="88"/>
+      <c r="B69" s="85"/>
       <c r="C69" s="13" t="s">
         <v>126</v>
       </c>
@@ -4516,8 +4503,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="99"/>
-      <c r="B70" s="89"/>
+      <c r="A70" s="88"/>
+      <c r="B70" s="85"/>
       <c r="C70" s="13" t="s">
         <v>127</v>
       </c>
@@ -4530,8 +4517,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="99"/>
-      <c r="B71" s="89"/>
+      <c r="A71" s="88"/>
+      <c r="B71" s="85"/>
       <c r="C71" s="13" t="s">
         <v>141</v>
       </c>
@@ -4544,8 +4531,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="99"/>
-      <c r="B72" s="89"/>
+      <c r="A72" s="88"/>
+      <c r="B72" s="85"/>
       <c r="C72" s="13" t="s">
         <v>155</v>
       </c>
@@ -4558,8 +4545,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="99"/>
-      <c r="B73" s="89"/>
+      <c r="A73" s="88"/>
+      <c r="B73" s="85"/>
       <c r="C73" s="13" t="s">
         <v>196</v>
       </c>
@@ -4572,8 +4559,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="99"/>
-      <c r="B74" s="89"/>
+      <c r="A74" s="88"/>
+      <c r="B74" s="85"/>
       <c r="C74" s="13" t="s">
         <v>167</v>
       </c>
@@ -4586,8 +4573,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="99"/>
-      <c r="B75" s="89"/>
+      <c r="A75" s="88"/>
+      <c r="B75" s="85"/>
       <c r="C75" s="13" t="s">
         <v>188</v>
       </c>
@@ -4600,18 +4587,18 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="100"/>
-      <c r="B76" s="109"/>
+      <c r="A76" s="93"/>
+      <c r="B76" s="95"/>
       <c r="C76" s="40"/>
       <c r="D76" s="40"/>
       <c r="E76" s="41"/>
       <c r="F76" s="40"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="93" t="s">
+      <c r="A77" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="95" t="s">
+      <c r="B77" s="89" t="s">
         <v>73</v>
       </c>
       <c r="C77" s="26" t="s">
@@ -4626,8 +4613,8 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="99"/>
-      <c r="B78" s="89"/>
+      <c r="A78" s="88"/>
+      <c r="B78" s="85"/>
       <c r="C78" s="13" t="s">
         <v>153</v>
       </c>
@@ -4640,13 +4627,13 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="99"/>
-      <c r="B79" s="90"/>
+      <c r="A79" s="88"/>
+      <c r="B79" s="86"/>
       <c r="E79" s="31"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="99"/>
-      <c r="B80" s="101" t="s">
+      <c r="A80" s="88"/>
+      <c r="B80" s="94" t="s">
         <v>4</v>
       </c>
       <c r="C80" s="35" t="s">
@@ -4661,8 +4648,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="99"/>
-      <c r="B81" s="87"/>
+      <c r="A81" s="88"/>
+      <c r="B81" s="83"/>
       <c r="C81" s="13" t="s">
         <v>107</v>
       </c>
@@ -4675,8 +4662,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="99"/>
-      <c r="B82" s="87"/>
+      <c r="A82" s="88"/>
+      <c r="B82" s="83"/>
       <c r="C82" s="13" t="s">
         <v>122</v>
       </c>
@@ -4689,8 +4676,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="99"/>
-      <c r="B83" s="87"/>
+      <c r="A83" s="88"/>
+      <c r="B83" s="83"/>
       <c r="C83" s="13" t="s">
         <v>141</v>
       </c>
@@ -4703,8 +4690,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="99"/>
-      <c r="B84" s="87"/>
+      <c r="A84" s="88"/>
+      <c r="B84" s="83"/>
       <c r="C84" s="13" t="s">
         <v>155</v>
       </c>
@@ -4717,8 +4704,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="99"/>
-      <c r="B85" s="87"/>
+      <c r="A85" s="88"/>
+      <c r="B85" s="83"/>
       <c r="C85" s="13" t="s">
         <v>161</v>
       </c>
@@ -4731,8 +4718,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="99"/>
-      <c r="B86" s="87"/>
+      <c r="A86" s="88"/>
+      <c r="B86" s="83"/>
       <c r="C86" s="13" t="s">
         <v>196</v>
       </c>
@@ -4745,8 +4732,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="99"/>
-      <c r="B87" s="87"/>
+      <c r="A87" s="88"/>
+      <c r="B87" s="83"/>
       <c r="C87" s="13" t="s">
         <v>167</v>
       </c>
@@ -4759,8 +4746,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="99"/>
-      <c r="B88" s="87"/>
+      <c r="A88" s="88"/>
+      <c r="B88" s="83"/>
       <c r="C88" s="13" t="s">
         <v>188</v>
       </c>
@@ -4773,12 +4760,12 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="99"/>
-      <c r="B89" s="102"/>
+      <c r="A89" s="88"/>
+      <c r="B89" s="97"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="99"/>
-      <c r="B90" s="101" t="s">
+      <c r="A90" s="88"/>
+      <c r="B90" s="94" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="35" t="s">
@@ -4793,8 +4780,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="99"/>
-      <c r="B91" s="87"/>
+      <c r="A91" s="88"/>
+      <c r="B91" s="83"/>
       <c r="C91" s="13" t="s">
         <v>108</v>
       </c>
@@ -4807,8 +4794,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="99"/>
-      <c r="B92" s="87"/>
+      <c r="A92" s="88"/>
+      <c r="B92" s="83"/>
       <c r="C92" s="13" t="s">
         <v>120</v>
       </c>
@@ -4821,8 +4808,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="99"/>
-      <c r="B93" s="87"/>
+      <c r="A93" s="88"/>
+      <c r="B93" s="83"/>
       <c r="C93" s="13" t="s">
         <v>141</v>
       </c>
@@ -4835,8 +4822,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="99"/>
-      <c r="B94" s="87"/>
+      <c r="A94" s="88"/>
+      <c r="B94" s="83"/>
       <c r="C94" s="13" t="s">
         <v>155</v>
       </c>
@@ -4849,8 +4836,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="99"/>
-      <c r="B95" s="87"/>
+      <c r="A95" s="88"/>
+      <c r="B95" s="83"/>
       <c r="C95" s="13" t="s">
         <v>161</v>
       </c>
@@ -4863,8 +4850,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="99"/>
-      <c r="B96" s="87"/>
+      <c r="A96" s="88"/>
+      <c r="B96" s="83"/>
       <c r="C96" s="13" t="s">
         <v>196</v>
       </c>
@@ -4877,8 +4864,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="99"/>
-      <c r="B97" s="87"/>
+      <c r="A97" s="88"/>
+      <c r="B97" s="83"/>
       <c r="C97" s="13" t="s">
         <v>167</v>
       </c>
@@ -4891,8 +4878,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="99"/>
-      <c r="B98" s="87"/>
+      <c r="A98" s="88"/>
+      <c r="B98" s="83"/>
       <c r="C98" s="13" t="s">
         <v>188</v>
       </c>
@@ -4905,14 +4892,14 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="100"/>
-      <c r="B99" s="103"/>
+      <c r="A99" s="93"/>
+      <c r="B99" s="99"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="93" t="s">
+      <c r="A100" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="B100" s="95" t="s">
+      <c r="B100" s="89" t="s">
         <v>73</v>
       </c>
       <c r="C100" s="26" t="s">
@@ -4927,8 +4914,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="99"/>
-      <c r="B101" s="89"/>
+      <c r="A101" s="88"/>
+      <c r="B101" s="85"/>
       <c r="C101" s="13" t="s">
         <v>228</v>
       </c>
@@ -4941,8 +4928,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="99"/>
-      <c r="B102" s="89"/>
+      <c r="A102" s="88"/>
+      <c r="B102" s="85"/>
       <c r="C102" s="13" t="s">
         <v>150</v>
       </c>
@@ -4955,16 +4942,16 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="99"/>
-      <c r="B103" s="90"/>
+      <c r="A103" s="88"/>
+      <c r="B103" s="86"/>
       <c r="C103" s="36"/>
       <c r="D103" s="36"/>
       <c r="E103" s="37"/>
       <c r="F103" s="36"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="99"/>
-      <c r="B104" s="88" t="s">
+      <c r="A104" s="88"/>
+      <c r="B104" s="84" t="s">
         <v>292</v>
       </c>
       <c r="C104" s="13" t="s">
@@ -4979,8 +4966,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="99"/>
-      <c r="B105" s="89"/>
+      <c r="A105" s="88"/>
+      <c r="B105" s="85"/>
       <c r="C105" s="13" t="s">
         <v>297</v>
       </c>
@@ -4993,8 +4980,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="99"/>
-      <c r="B106" s="89"/>
+      <c r="A106" s="88"/>
+      <c r="B106" s="85"/>
       <c r="C106" s="13" t="s">
         <v>298</v>
       </c>
@@ -5007,13 +4994,13 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="99"/>
-      <c r="B107" s="90"/>
+      <c r="A107" s="88"/>
+      <c r="B107" s="86"/>
       <c r="E107" s="33"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="99"/>
-      <c r="B108" s="88" t="s">
+      <c r="A108" s="88"/>
+      <c r="B108" s="84" t="s">
         <v>79</v>
       </c>
       <c r="C108" s="35" t="s">
@@ -5028,30 +5015,30 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="99"/>
-      <c r="B109" s="91"/>
-      <c r="C109" s="70" t="s">
+      <c r="A109" s="88"/>
+      <c r="B109" s="85"/>
+      <c r="C109" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D109" s="70" t="s">
+      <c r="D109" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="E109" s="71"/>
-      <c r="F109" s="70" t="s">
+      <c r="E109" s="33"/>
+      <c r="F109" s="13" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="99"/>
-      <c r="B110" s="90"/>
+      <c r="A110" s="88"/>
+      <c r="B110" s="86"/>
       <c r="C110" s="36"/>
       <c r="D110" s="36"/>
       <c r="E110" s="37"/>
       <c r="F110" s="36"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="99"/>
-      <c r="B111" s="104" t="s">
+      <c r="A111" s="88"/>
+      <c r="B111" s="100" t="s">
         <v>371</v>
       </c>
       <c r="C111" s="35" t="s">
@@ -5066,30 +5053,30 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="99"/>
-      <c r="B112" s="105"/>
-      <c r="C112" s="70" t="s">
+      <c r="A112" s="88"/>
+      <c r="B112" s="101"/>
+      <c r="C112" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="D112" s="70" t="s">
+      <c r="D112" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="E112" s="71"/>
-      <c r="F112" s="70" t="s">
+      <c r="E112" s="33"/>
+      <c r="F112" s="13" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="99"/>
-      <c r="B113" s="106"/>
+      <c r="A113" s="88"/>
+      <c r="B113" s="102"/>
       <c r="C113" s="36"/>
       <c r="D113" s="36"/>
       <c r="E113" s="37"/>
       <c r="F113" s="36"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="99"/>
-      <c r="B114" s="96" t="s">
+      <c r="A114" s="88"/>
+      <c r="B114" s="91" t="s">
         <v>331</v>
       </c>
       <c r="C114" s="13" t="s">
@@ -5104,8 +5091,8 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="99"/>
-      <c r="B115" s="97"/>
+      <c r="A115" s="88"/>
+      <c r="B115" s="91"/>
       <c r="C115" s="13" t="s">
         <v>362</v>
       </c>
@@ -5118,7 +5105,7 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="100"/>
+      <c r="A116" s="93"/>
       <c r="B116" s="98"/>
       <c r="C116" s="40"/>
       <c r="D116" s="40"/>
@@ -5126,10 +5113,10 @@
       <c r="F116" s="40"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="93" t="s">
+      <c r="A117" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="B117" s="95" t="s">
+      <c r="B117" s="89" t="s">
         <v>13</v>
       </c>
       <c r="C117" s="26" t="s">
@@ -5144,8 +5131,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="94"/>
-      <c r="B118" s="91"/>
+      <c r="A118" s="88"/>
+      <c r="B118" s="85"/>
       <c r="C118" s="13" t="s">
         <v>174</v>
       </c>
@@ -5157,16 +5144,16 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="94"/>
-      <c r="B119" s="90"/>
+      <c r="A119" s="88"/>
+      <c r="B119" s="86"/>
       <c r="C119" s="36"/>
       <c r="D119" s="36"/>
       <c r="E119" s="36"/>
       <c r="F119" s="36"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="94"/>
-      <c r="B120" s="88" t="s">
+      <c r="A120" s="88"/>
+      <c r="B120" s="84" t="s">
         <v>183</v>
       </c>
       <c r="C120" s="13" t="s">
@@ -5180,8 +5167,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="94"/>
-      <c r="B121" s="91"/>
+      <c r="A121" s="88"/>
+      <c r="B121" s="85"/>
       <c r="C121" s="13" t="s">
         <v>181</v>
       </c>
@@ -5193,8 +5180,8 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="94"/>
-      <c r="B122" s="91"/>
+      <c r="A122" s="88"/>
+      <c r="B122" s="85"/>
       <c r="C122" s="13" t="s">
         <v>177</v>
       </c>
@@ -5206,8 +5193,8 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="94"/>
-      <c r="B123" s="91"/>
+      <c r="A123" s="88"/>
+      <c r="B123" s="85"/>
       <c r="C123" s="13" t="s">
         <v>179</v>
       </c>
@@ -5219,8 +5206,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="94"/>
-      <c r="B124" s="91"/>
+      <c r="A124" s="88"/>
+      <c r="B124" s="85"/>
       <c r="C124" s="13" t="s">
         <v>182</v>
       </c>
@@ -5232,8 +5219,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="94"/>
-      <c r="B125" s="91"/>
+      <c r="A125" s="88"/>
+      <c r="B125" s="85"/>
       <c r="C125" s="13" t="s">
         <v>191</v>
       </c>
@@ -5245,12 +5232,12 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="94"/>
-      <c r="B126" s="90"/>
+      <c r="A126" s="88"/>
+      <c r="B126" s="86"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="94"/>
-      <c r="B127" s="88" t="s">
+      <c r="A127" s="88"/>
+      <c r="B127" s="84" t="s">
         <v>206</v>
       </c>
       <c r="C127" s="35" t="s">
@@ -5265,8 +5252,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="94"/>
-      <c r="B128" s="91"/>
+      <c r="A128" s="88"/>
+      <c r="B128" s="85"/>
       <c r="C128" s="13" t="s">
         <v>204</v>
       </c>
@@ -5278,8 +5265,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="94"/>
-      <c r="B129" s="91"/>
+      <c r="A129" s="88"/>
+      <c r="B129" s="85"/>
       <c r="C129" s="13" t="s">
         <v>215</v>
       </c>
@@ -5291,8 +5278,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="94"/>
-      <c r="B130" s="91"/>
+      <c r="A130" s="88"/>
+      <c r="B130" s="85"/>
       <c r="C130" s="13" t="s">
         <v>205</v>
       </c>
@@ -5304,8 +5291,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="94"/>
-      <c r="B131" s="91"/>
+      <c r="A131" s="88"/>
+      <c r="B131" s="85"/>
       <c r="C131" s="13" t="s">
         <v>300</v>
       </c>
@@ -5317,8 +5304,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="94"/>
-      <c r="B132" s="91"/>
+      <c r="A132" s="88"/>
+      <c r="B132" s="85"/>
       <c r="C132" s="44" t="s">
         <v>324</v>
       </c>
@@ -5331,8 +5318,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="94"/>
-      <c r="B133" s="91"/>
+      <c r="A133" s="88"/>
+      <c r="B133" s="85"/>
       <c r="C133" s="44" t="s">
         <v>326</v>
       </c>
@@ -5345,8 +5332,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="94"/>
-      <c r="B134" s="91"/>
+      <c r="A134" s="88"/>
+      <c r="B134" s="85"/>
       <c r="C134" s="13" t="s">
         <v>217</v>
       </c>
@@ -5358,8 +5345,8 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="94"/>
-      <c r="B135" s="91"/>
+      <c r="A135" s="88"/>
+      <c r="B135" s="85"/>
       <c r="C135" s="13" t="s">
         <v>221</v>
       </c>
@@ -5371,8 +5358,8 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="94"/>
-      <c r="B136" s="91"/>
+      <c r="A136" s="88"/>
+      <c r="B136" s="85"/>
       <c r="C136" s="13" t="s">
         <v>202</v>
       </c>
@@ -5384,8 +5371,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="94"/>
-      <c r="B137" s="91"/>
+      <c r="A137" s="88"/>
+      <c r="B137" s="85"/>
       <c r="C137" s="44" t="s">
         <v>249</v>
       </c>
@@ -5398,8 +5385,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="94"/>
-      <c r="B138" s="91"/>
+      <c r="A138" s="88"/>
+      <c r="B138" s="85"/>
       <c r="C138" s="44" t="s">
         <v>383</v>
       </c>
@@ -5412,8 +5399,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="94"/>
-      <c r="B139" s="91"/>
+      <c r="A139" s="88"/>
+      <c r="B139" s="85"/>
       <c r="C139" s="44" t="s">
         <v>365</v>
       </c>
@@ -5426,8 +5413,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="94"/>
-      <c r="B140" s="91"/>
+      <c r="A140" s="88"/>
+      <c r="B140" s="85"/>
       <c r="C140" s="44" t="s">
         <v>385</v>
       </c>
@@ -5440,16 +5427,16 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="94"/>
-      <c r="B141" s="90"/>
+      <c r="A141" s="88"/>
+      <c r="B141" s="86"/>
       <c r="C141" s="44"/>
       <c r="D141" s="44"/>
       <c r="E141" s="44"/>
       <c r="F141" s="44"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="94"/>
-      <c r="B142" s="88" t="s">
+      <c r="A142" s="88"/>
+      <c r="B142" s="84" t="s">
         <v>222</v>
       </c>
       <c r="C142" s="35" t="s">
@@ -5464,116 +5451,103 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="94"/>
-      <c r="B143" s="91"/>
-      <c r="C143" s="70" t="s">
+      <c r="A143" s="88"/>
+      <c r="B143" s="85"/>
+      <c r="C143" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="D143" s="70" t="s">
+      <c r="D143" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="E143" s="70"/>
-      <c r="F143" s="70" t="s">
+      <c r="F143" s="13" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="94"/>
-      <c r="B144" s="91"/>
-      <c r="C144" s="70" t="s">
+      <c r="A144" s="88"/>
+      <c r="B144" s="85"/>
+      <c r="C144" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="D144" s="70" t="s">
+      <c r="D144" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E144" s="70"/>
-      <c r="F144" s="70" t="s">
+      <c r="F144" s="13" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="94"/>
-      <c r="B145" s="91"/>
-      <c r="C145" s="72" t="s">
+      <c r="A145" s="88"/>
+      <c r="B145" s="85"/>
+      <c r="C145" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="D145" s="72" t="s">
+      <c r="D145" s="44" t="s">
         <v>252</v>
       </c>
-      <c r="E145" s="72"/>
-      <c r="F145" s="72" t="s">
+      <c r="E145" s="44"/>
+      <c r="F145" s="44" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="94"/>
-      <c r="B146" s="91"/>
-      <c r="C146" s="72" t="s">
+      <c r="A146" s="88"/>
+      <c r="B146" s="85"/>
+      <c r="C146" s="44" t="s">
         <v>366</v>
       </c>
-      <c r="D146" s="72" t="s">
+      <c r="D146" s="44" t="s">
         <v>367</v>
       </c>
-      <c r="E146" s="72"/>
-      <c r="F146" s="72" t="s">
+      <c r="E146" s="44"/>
+      <c r="F146" s="44" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="94"/>
-      <c r="B147" s="90"/>
+      <c r="A147" s="88"/>
+      <c r="B147" s="86"/>
       <c r="C147" s="36"/>
       <c r="D147" s="36"/>
       <c r="E147" s="36"/>
       <c r="F147" s="36"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="94"/>
-      <c r="B148" s="92" t="s">
+      <c r="A148" s="88"/>
+      <c r="B148" s="103" t="s">
         <v>386</v>
       </c>
-      <c r="C148" s="70" t="s">
+      <c r="C148" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="D148" s="70" t="s">
+      <c r="D148" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="E148" s="70"/>
-      <c r="F148" s="70" t="s">
+      <c r="F148" s="13" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="94"/>
-      <c r="B149" s="92"/>
-      <c r="C149" s="70" t="s">
+      <c r="A149" s="88"/>
+      <c r="B149" s="103"/>
+      <c r="C149" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="D149" s="70" t="s">
+      <c r="D149" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="E149" s="70"/>
-      <c r="F149" s="70" t="s">
+      <c r="F149" s="13" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C150" s="70"/>
-      <c r="D150" s="70"/>
-      <c r="E150" s="70"/>
-      <c r="F150" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="B34:B44"/>
-    <mergeCell ref="A45:A76"/>
-    <mergeCell ref="B65:B76"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B45:B54"/>
-    <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A117:A149"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="B120:B126"/>
     <mergeCell ref="B114:B116"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A77:A99"/>
@@ -5584,12 +5558,15 @@
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A117:A149"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="A2:A44"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="B34:B44"/>
+    <mergeCell ref="A45:A76"/>
+    <mergeCell ref="B65:B76"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B45:B54"/>
+    <mergeCell ref="B55:B64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Fischer_Tropsch/FischerTropsch_Naphta_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Naphta_Greenfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Greenfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215824B0-835F-40C1-8D67-D6671FAC6B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3A10BC-1897-49A2-BC8F-33DDF78B4F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-2400" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="390">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -875,12 +875,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>CO2-Bereitstellung / Direct Air Capture</t>
   </si>
   <si>
@@ -1079,13 +1073,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1381,10 +1369,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1593,21 +1581,21 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1615,10 +1603,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1630,27 +1618,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1660,21 +1648,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1730,6 +1718,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1739,13 +1730,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1754,17 +1742,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1778,8 +1757,17 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2416,19 +2404,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="70"/>
       <c r="B8" s="80" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E8" s="66">
         <v>38.99</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2438,7 +2426,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E9" s="65">
         <v>285.39999999999998</v>
@@ -2454,13 +2442,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E10" s="65">
         <v>2440</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2470,7 +2458,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E11" s="64">
         <v>0.03</v>
@@ -2486,45 +2474,45 @@
         <v>86</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E12" s="65">
         <v>0.63</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="70"/>
       <c r="B13" s="81"/>
       <c r="C13" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E13" s="65">
         <v>4.8600000000000003</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="70"/>
       <c r="B14" s="81"/>
       <c r="C14" s="13" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E14" s="65">
         <v>0.39</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2534,7 +2522,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E15" s="62">
         <v>20</v>
@@ -2550,7 +2538,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E16" s="63">
         <v>7.0000000000000007E-2</v>
@@ -2562,13 +2550,13 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="70"/>
       <c r="B17" s="84" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C17" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E17" s="53">
         <v>3.7</v>
@@ -2584,13 +2572,13 @@
         <v>84</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E18" s="54">
         <v>0.27</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2600,13 +2588,13 @@
         <v>10</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E19" s="54">
         <v>700</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2616,7 +2604,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E20" s="54">
         <v>0.02</v>
@@ -2632,7 +2620,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E21" s="54">
         <v>20</v>
@@ -2648,7 +2636,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E22" s="55">
         <v>0.05</v>
@@ -2660,35 +2648,35 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="70"/>
       <c r="B23" s="83" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C23" s="44" t="s">
         <v>84</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E23" s="46">
         <v>0.5</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="70"/>
       <c r="B24" s="83"/>
       <c r="C24" s="44" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E24" s="46">
         <v>1.75</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2698,13 +2686,13 @@
         <v>10</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E25" s="46">
         <v>7000</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2714,7 +2702,7 @@
         <v>11</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E26" s="47">
         <v>0.05</v>
@@ -2730,7 +2718,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E27" s="48">
         <v>15</v>
@@ -2746,7 +2734,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E28" s="47">
         <v>7.0000000000000007E-2</v>
@@ -2890,19 +2878,19 @@
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="70"/>
       <c r="B37" s="75" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C37" s="26" t="s">
         <v>87</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E37" s="38">
         <v>2.83</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2912,7 +2900,7 @@
         <v>11</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E38" s="33">
         <v>0.03</v>
@@ -2928,7 +2916,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E39" s="34">
         <v>30</v>
@@ -2944,7 +2932,7 @@
         <v>20</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E40" s="33">
         <v>7.3999999999999999E-4</v>
@@ -2960,7 +2948,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E41" s="33">
         <v>0.98</v>
@@ -2976,7 +2964,7 @@
         <v>36</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E42" s="33">
         <v>0.98</v>
@@ -2992,7 +2980,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E43" s="33">
         <v>0.05</v>
@@ -3008,7 +2996,7 @@
         <v>88</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E44" s="37">
         <v>0</v>
@@ -3442,7 +3430,7 @@
         <v>78</v>
       </c>
       <c r="E70" s="58">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="57" t="s">
         <v>19</v>
@@ -3451,19 +3439,19 @@
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="70"/>
       <c r="B71" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C71" t="s">
+        <v>287</v>
+      </c>
+      <c r="D71" t="s">
         <v>288</v>
       </c>
-      <c r="C71" t="s">
-        <v>289</v>
-      </c>
-      <c r="D71" t="s">
-        <v>290</v>
-      </c>
       <c r="E71" s="7">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3487,38 +3475,38 @@
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="70"/>
       <c r="B73" s="17" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E73" s="19">
         <v>-0.55000000000000004</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="71"/>
       <c r="B74" s="61" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E74" s="67">
         <f>-2.2</f>
         <v>-2.2000000000000002</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -3545,7 +3533,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
@@ -3578,10 +3566,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="90" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3596,7 +3584,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="88"/>
+      <c r="A3" s="89"/>
       <c r="B3" s="85"/>
       <c r="C3" s="13" t="s">
         <v>107</v>
@@ -3610,7 +3598,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="88"/>
+      <c r="A4" s="89"/>
       <c r="B4" s="85"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
@@ -3624,7 +3612,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="88"/>
+      <c r="A5" s="89"/>
       <c r="B5" s="85"/>
       <c r="C5" s="13" t="s">
         <v>138</v>
@@ -3638,7 +3626,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
+      <c r="A6" s="89"/>
       <c r="B6" s="85"/>
       <c r="C6" s="13" t="s">
         <v>141</v>
@@ -3652,7 +3640,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="85"/>
       <c r="C7" s="13" t="s">
         <v>155</v>
@@ -3666,7 +3654,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
+      <c r="A8" s="89"/>
       <c r="B8" s="85"/>
       <c r="C8" s="13" t="s">
         <v>196</v>
@@ -3680,7 +3668,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
+      <c r="A9" s="89"/>
       <c r="B9" s="85"/>
       <c r="C9" s="13" t="s">
         <v>167</v>
@@ -3694,7 +3682,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
+      <c r="A10" s="89"/>
       <c r="B10" s="85"/>
       <c r="C10" s="13" t="s">
         <v>188</v>
@@ -3708,20 +3696,20 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
+      <c r="A11" s="89"/>
       <c r="B11" s="85"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="90" t="s">
-        <v>364</v>
+      <c r="A12" s="89"/>
+      <c r="B12" s="100" t="s">
+        <v>360</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E12" s="68"/>
       <c r="F12" s="35" t="s">
@@ -3729,41 +3717,41 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
+      <c r="A13" s="89"/>
       <c r="B13" s="91"/>
       <c r="C13" s="13" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="13" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
+      <c r="A14" s="89"/>
       <c r="B14" s="91"/>
       <c r="C14" s="13" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="13" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
+      <c r="A15" s="89"/>
       <c r="B15" s="91"/>
       <c r="C15" s="13" t="s">
         <v>139</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="31" t="s">
@@ -3771,27 +3759,27 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="88"/>
+      <c r="A16" s="89"/>
       <c r="B16" s="91"/>
       <c r="C16" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E16" s="33"/>
       <c r="F16" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="88"/>
+      <c r="A17" s="89"/>
       <c r="B17" s="91"/>
       <c r="C17" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="13" t="s">
@@ -3799,13 +3787,13 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="88"/>
+      <c r="A18" s="89"/>
       <c r="B18" s="91"/>
       <c r="C18" s="13" t="s">
         <v>141</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="13" t="s">
@@ -3813,13 +3801,13 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="88"/>
+      <c r="A19" s="89"/>
       <c r="B19" s="91"/>
       <c r="C19" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="13" t="s">
@@ -3827,13 +3815,13 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="88"/>
+      <c r="A20" s="89"/>
       <c r="B20" s="91"/>
       <c r="C20" s="13" t="s">
         <v>196</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="13" t="s">
@@ -3841,13 +3829,13 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
+      <c r="A21" s="89"/>
       <c r="B21" s="91"/>
       <c r="C21" s="13" t="s">
         <v>167</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="13" t="s">
@@ -3855,13 +3843,13 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="88"/>
+      <c r="A22" s="89"/>
       <c r="B22" s="91"/>
       <c r="C22" s="13" t="s">
         <v>188</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="13" t="s">
@@ -3869,37 +3857,37 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="92"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="101"/>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
       <c r="F23" s="36"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="88"/>
+      <c r="A24" s="89"/>
       <c r="B24" s="84" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>96</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
+      <c r="A25" s="89"/>
       <c r="B25" s="85"/>
       <c r="C25" s="13" t="s">
         <v>107</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E25" s="31"/>
       <c r="F25" s="13" t="s">
@@ -3907,41 +3895,41 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
+      <c r="A26" s="89"/>
       <c r="B26" s="85"/>
       <c r="C26" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E26" s="33"/>
       <c r="F26" s="13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
+      <c r="A27" s="89"/>
       <c r="B27" s="85"/>
       <c r="C27" s="13" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
+      <c r="A28" s="89"/>
       <c r="B28" s="85"/>
       <c r="C28" s="13" t="s">
         <v>141</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E28" s="34"/>
       <c r="F28" s="13" t="s">
@@ -3949,13 +3937,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
+      <c r="A29" s="89"/>
       <c r="B29" s="85"/>
       <c r="C29" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E29" s="34"/>
       <c r="F29" s="13" t="s">
@@ -3963,13 +3951,13 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="88"/>
+      <c r="A30" s="89"/>
       <c r="B30" s="85"/>
       <c r="C30" s="13" t="s">
         <v>196</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E30" s="34"/>
       <c r="F30" s="13" t="s">
@@ -3977,13 +3965,13 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="88"/>
+      <c r="A31" s="89"/>
       <c r="B31" s="85"/>
       <c r="C31" s="13" t="s">
         <v>167</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E31" s="33"/>
       <c r="F31" s="13" t="s">
@@ -3991,13 +3979,13 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="88"/>
+      <c r="A32" s="89"/>
       <c r="B32" s="85"/>
       <c r="C32" s="13" t="s">
         <v>188</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E32" s="33"/>
       <c r="F32" s="13" t="s">
@@ -4005,7 +3993,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="88"/>
+      <c r="A33" s="89"/>
       <c r="B33" s="86"/>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
@@ -4013,15 +4001,15 @@
       <c r="F33" s="36"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="88"/>
+      <c r="A34" s="89"/>
       <c r="B34" s="83" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>96</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E34" s="31"/>
       <c r="F34" s="13" t="s">
@@ -4029,13 +4017,13 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="88"/>
+      <c r="A35" s="89"/>
       <c r="B35" s="83"/>
       <c r="C35" s="13" t="s">
         <v>107</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E35" s="31"/>
       <c r="F35" s="13" t="s">
@@ -4043,13 +4031,13 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="88"/>
+      <c r="A36" s="89"/>
       <c r="B36" s="83"/>
       <c r="C36" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E36" s="33"/>
       <c r="F36" s="13" t="s">
@@ -4057,41 +4045,41 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="88"/>
+      <c r="A37" s="89"/>
       <c r="B37" s="83"/>
       <c r="C37" s="13" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E37" s="33"/>
       <c r="F37" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="88"/>
+      <c r="A38" s="89"/>
       <c r="B38" s="83"/>
       <c r="C38" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="88"/>
+      <c r="A39" s="89"/>
       <c r="B39" s="83"/>
       <c r="C39" s="13" t="s">
         <v>141</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E39" s="34"/>
       <c r="F39" s="13" t="s">
@@ -4099,13 +4087,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="88"/>
+      <c r="A40" s="89"/>
       <c r="B40" s="83"/>
       <c r="C40" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E40" s="34"/>
       <c r="F40" s="13" t="s">
@@ -4113,13 +4101,13 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="88"/>
+      <c r="A41" s="89"/>
       <c r="B41" s="83"/>
       <c r="C41" s="13" t="s">
         <v>196</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E41" s="34"/>
       <c r="F41" s="13" t="s">
@@ -4127,13 +4115,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="88"/>
+      <c r="A42" s="89"/>
       <c r="B42" s="83"/>
       <c r="C42" s="13" t="s">
         <v>167</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E42" s="33"/>
       <c r="F42" s="13" t="s">
@@ -4141,13 +4129,13 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="88"/>
+      <c r="A43" s="89"/>
       <c r="B43" s="83"/>
       <c r="C43" s="13" t="s">
         <v>188</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E43" s="33"/>
       <c r="F43" s="13" t="s">
@@ -4155,15 +4143,15 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="88"/>
+      <c r="A44" s="89"/>
       <c r="B44" s="83"/>
       <c r="E44" s="33"/>
     </row>
     <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="87" t="s">
+      <c r="A45" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="96" t="s">
+      <c r="B45" s="103" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="26" t="s">
@@ -4174,11 +4162,11 @@
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="88"/>
+      <c r="A46" s="89"/>
       <c r="B46" s="83"/>
       <c r="C46" s="13" t="s">
         <v>111</v>
@@ -4188,11 +4176,11 @@
       </c>
       <c r="E46" s="33"/>
       <c r="F46" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="88"/>
+      <c r="A47" s="89"/>
       <c r="B47" s="83"/>
       <c r="C47" s="13" t="s">
         <v>135</v>
@@ -4206,7 +4194,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="88"/>
+      <c r="A48" s="89"/>
       <c r="B48" s="83"/>
       <c r="C48" s="13" t="s">
         <v>136</v>
@@ -4220,7 +4208,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="88"/>
+      <c r="A49" s="89"/>
       <c r="B49" s="83"/>
       <c r="C49" s="13" t="s">
         <v>141</v>
@@ -4234,7 +4222,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="88"/>
+      <c r="A50" s="89"/>
       <c r="B50" s="83"/>
       <c r="C50" s="13" t="s">
         <v>155</v>
@@ -4248,7 +4236,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="88"/>
+      <c r="A51" s="89"/>
       <c r="B51" s="83"/>
       <c r="C51" s="13" t="s">
         <v>196</v>
@@ -4262,7 +4250,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="88"/>
+      <c r="A52" s="89"/>
       <c r="B52" s="83"/>
       <c r="C52" s="13" t="s">
         <v>167</v>
@@ -4276,7 +4264,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="88"/>
+      <c r="A53" s="89"/>
       <c r="B53" s="83"/>
       <c r="C53" s="13" t="s">
         <v>188</v>
@@ -4290,79 +4278,79 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="88"/>
-      <c r="B54" s="97"/>
+      <c r="A54" s="89"/>
+      <c r="B54" s="95"/>
       <c r="C54" s="36"/>
       <c r="D54" s="36"/>
       <c r="E54" s="37"/>
       <c r="F54" s="36"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="88"/>
+      <c r="A55" s="89"/>
       <c r="B55" s="83" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>113</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E55" s="31"/>
       <c r="F55" s="13" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="88"/>
+      <c r="A56" s="89"/>
       <c r="B56" s="83"/>
       <c r="C56" s="13" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E56" s="33"/>
       <c r="F56" s="13" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="88"/>
+      <c r="A57" s="89"/>
       <c r="B57" s="83"/>
       <c r="C57" s="13" t="s">
         <v>135</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E57" s="34"/>
       <c r="F57" s="13" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="88"/>
+      <c r="A58" s="89"/>
       <c r="B58" s="83"/>
       <c r="C58" s="13" t="s">
         <v>136</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E58" s="33"/>
       <c r="F58" s="13" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="88"/>
+      <c r="A59" s="89"/>
       <c r="B59" s="83"/>
       <c r="C59" s="13" t="s">
         <v>141</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E59" s="33"/>
       <c r="F59" s="13" t="s">
@@ -4370,13 +4358,13 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="88"/>
+      <c r="A60" s="89"/>
       <c r="B60" s="83"/>
       <c r="C60" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E60" s="33"/>
       <c r="F60" s="13" t="s">
@@ -4384,13 +4372,13 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="88"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="83"/>
       <c r="C61" s="13" t="s">
         <v>196</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E61" s="33"/>
       <c r="F61" s="13" t="s">
@@ -4398,13 +4386,13 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="88"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="83"/>
       <c r="C62" s="13" t="s">
         <v>167</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E62" s="33"/>
       <c r="F62" s="13" t="s">
@@ -4412,13 +4400,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="88"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="83"/>
       <c r="C63" s="13" t="s">
         <v>188</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E63" s="33"/>
       <c r="F63" s="13" t="s">
@@ -4426,12 +4414,12 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="88"/>
-      <c r="B64" s="97"/>
+      <c r="A64" s="89"/>
+      <c r="B64" s="95"/>
       <c r="E64" s="33"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="88"/>
+      <c r="A65" s="89"/>
       <c r="B65" s="94" t="s">
         <v>6</v>
       </c>
@@ -4447,7 +4435,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="88"/>
+      <c r="A66" s="89"/>
       <c r="B66" s="83"/>
       <c r="C66" s="13" t="s">
         <v>113</v>
@@ -4461,7 +4449,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="88"/>
+      <c r="A67" s="89"/>
       <c r="B67" s="85"/>
       <c r="C67" s="13" t="s">
         <v>111</v>
@@ -4475,7 +4463,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="88"/>
+      <c r="A68" s="89"/>
       <c r="B68" s="85"/>
       <c r="C68" s="13" t="s">
         <v>107</v>
@@ -4489,7 +4477,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="85"/>
       <c r="C69" s="13" t="s">
         <v>126</v>
@@ -4503,7 +4491,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="85"/>
       <c r="C70" s="13" t="s">
         <v>127</v>
@@ -4517,7 +4505,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="85"/>
       <c r="C71" s="13" t="s">
         <v>141</v>
@@ -4531,7 +4519,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="85"/>
       <c r="C72" s="13" t="s">
         <v>155</v>
@@ -4545,7 +4533,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="88"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="85"/>
       <c r="C73" s="13" t="s">
         <v>196</v>
@@ -4559,7 +4547,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="88"/>
+      <c r="A74" s="89"/>
       <c r="B74" s="85"/>
       <c r="C74" s="13" t="s">
         <v>167</v>
@@ -4573,7 +4561,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="88"/>
+      <c r="A75" s="89"/>
       <c r="B75" s="85"/>
       <c r="C75" s="13" t="s">
         <v>188</v>
@@ -4588,17 +4576,17 @@
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="93"/>
-      <c r="B76" s="95"/>
+      <c r="B76" s="102"/>
       <c r="C76" s="40"/>
       <c r="D76" s="40"/>
       <c r="E76" s="41"/>
       <c r="F76" s="40"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="87" t="s">
+      <c r="A77" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="89" t="s">
+      <c r="B77" s="90" t="s">
         <v>73</v>
       </c>
       <c r="C77" s="26" t="s">
@@ -4613,7 +4601,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="88"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="85"/>
       <c r="C78" s="13" t="s">
         <v>153</v>
@@ -4627,12 +4615,12 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="88"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="86"/>
       <c r="E79" s="31"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="88"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="94" t="s">
         <v>4</v>
       </c>
@@ -4648,7 +4636,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="88"/>
+      <c r="A81" s="89"/>
       <c r="B81" s="83"/>
       <c r="C81" s="13" t="s">
         <v>107</v>
@@ -4662,7 +4650,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="88"/>
+      <c r="A82" s="89"/>
       <c r="B82" s="83"/>
       <c r="C82" s="13" t="s">
         <v>122</v>
@@ -4676,7 +4664,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="88"/>
+      <c r="A83" s="89"/>
       <c r="B83" s="83"/>
       <c r="C83" s="13" t="s">
         <v>141</v>
@@ -4690,7 +4678,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="88"/>
+      <c r="A84" s="89"/>
       <c r="B84" s="83"/>
       <c r="C84" s="13" t="s">
         <v>155</v>
@@ -4704,7 +4692,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="88"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="83"/>
       <c r="C85" s="13" t="s">
         <v>161</v>
@@ -4718,7 +4706,7 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="88"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="83"/>
       <c r="C86" s="13" t="s">
         <v>196</v>
@@ -4732,7 +4720,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="88"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="83"/>
       <c r="C87" s="13" t="s">
         <v>167</v>
@@ -4746,7 +4734,7 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="88"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="83"/>
       <c r="C88" s="13" t="s">
         <v>188</v>
@@ -4760,11 +4748,11 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="88"/>
-      <c r="B89" s="97"/>
+      <c r="A89" s="89"/>
+      <c r="B89" s="95"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="88"/>
+      <c r="A90" s="89"/>
       <c r="B90" s="94" t="s">
         <v>5</v>
       </c>
@@ -4780,7 +4768,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="88"/>
+      <c r="A91" s="89"/>
       <c r="B91" s="83"/>
       <c r="C91" s="13" t="s">
         <v>108</v>
@@ -4794,7 +4782,7 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="88"/>
+      <c r="A92" s="89"/>
       <c r="B92" s="83"/>
       <c r="C92" s="13" t="s">
         <v>120</v>
@@ -4808,7 +4796,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="88"/>
+      <c r="A93" s="89"/>
       <c r="B93" s="83"/>
       <c r="C93" s="13" t="s">
         <v>141</v>
@@ -4822,7 +4810,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="88"/>
+      <c r="A94" s="89"/>
       <c r="B94" s="83"/>
       <c r="C94" s="13" t="s">
         <v>155</v>
@@ -4836,7 +4824,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="88"/>
+      <c r="A95" s="89"/>
       <c r="B95" s="83"/>
       <c r="C95" s="13" t="s">
         <v>161</v>
@@ -4850,7 +4838,7 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="88"/>
+      <c r="A96" s="89"/>
       <c r="B96" s="83"/>
       <c r="C96" s="13" t="s">
         <v>196</v>
@@ -4864,7 +4852,7 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="88"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="83"/>
       <c r="C97" s="13" t="s">
         <v>167</v>
@@ -4878,7 +4866,7 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="88"/>
+      <c r="A98" s="89"/>
       <c r="B98" s="83"/>
       <c r="C98" s="13" t="s">
         <v>188</v>
@@ -4893,13 +4881,13 @@
     </row>
     <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="93"/>
-      <c r="B99" s="99"/>
+      <c r="B99" s="96"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="87" t="s">
+      <c r="A100" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="B100" s="89" t="s">
+      <c r="B100" s="90" t="s">
         <v>73</v>
       </c>
       <c r="C100" s="26" t="s">
@@ -4914,13 +4902,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="88"/>
+      <c r="A101" s="89"/>
       <c r="B101" s="85"/>
       <c r="C101" s="13" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E101" s="33"/>
       <c r="F101" s="13" t="s">
@@ -4928,470 +4916,470 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="88"/>
-      <c r="B102" s="85"/>
-      <c r="C102" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E102" s="33"/>
-      <c r="F102" s="13" t="s">
-        <v>149</v>
-      </c>
+      <c r="A102" s="89"/>
+      <c r="B102" s="86"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="37"/>
+      <c r="F102" s="36"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="88"/>
-      <c r="B103" s="86"/>
-      <c r="C103" s="36"/>
-      <c r="D103" s="36"/>
-      <c r="E103" s="37"/>
-      <c r="F103" s="36"/>
+      <c r="A103" s="89"/>
+      <c r="B103" s="84" t="s">
+        <v>290</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="E103" s="33"/>
+      <c r="F103" s="13" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="88"/>
-      <c r="B104" s="84" t="s">
-        <v>292</v>
-      </c>
+      <c r="A104" s="89"/>
+      <c r="B104" s="85"/>
       <c r="C104" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="D104" s="13" t="s">
         <v>293</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>294</v>
       </c>
       <c r="E104" s="33"/>
       <c r="F104" s="13" t="s">
-        <v>282</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="88"/>
-      <c r="B105" s="85"/>
-      <c r="C105" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>295</v>
-      </c>
+      <c r="A105" s="89"/>
+      <c r="B105" s="86"/>
       <c r="E105" s="33"/>
-      <c r="F105" s="13" t="s">
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="89"/>
+      <c r="B106" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="C106" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D106" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="E106" s="39"/>
+      <c r="F106" s="35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="89"/>
+      <c r="B107" s="85"/>
+      <c r="C107" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E107" s="33"/>
+      <c r="F107" s="13" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="88"/>
-      <c r="B106" s="85"/>
-      <c r="C106" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="E106" s="33"/>
-      <c r="F106" s="13" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="89"/>
+      <c r="B108" s="86"/>
+      <c r="C108" s="36"/>
+      <c r="D108" s="36"/>
+      <c r="E108" s="37"/>
+      <c r="F108" s="36"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="89"/>
+      <c r="B109" s="97" t="s">
+        <v>367</v>
+      </c>
+      <c r="C109" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="D109" s="35" t="s">
+        <v>374</v>
+      </c>
+      <c r="E109" s="39"/>
+      <c r="F109" s="35" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="89"/>
+      <c r="B110" s="98"/>
+      <c r="C110" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="E110" s="33"/>
+      <c r="F110" s="13" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="88"/>
-      <c r="B107" s="86"/>
-      <c r="E107" s="33"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="88"/>
-      <c r="B108" s="84" t="s">
-        <v>79</v>
-      </c>
-      <c r="C108" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D108" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="E108" s="39"/>
-      <c r="F108" s="35" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="88"/>
-      <c r="B109" s="85"/>
-      <c r="C109" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="E109" s="33"/>
-      <c r="F109" s="13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="88"/>
-      <c r="B110" s="86"/>
-      <c r="C110" s="36"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="37"/>
-      <c r="F110" s="36"/>
-    </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="88"/>
-      <c r="B111" s="100" t="s">
-        <v>371</v>
-      </c>
-      <c r="C111" s="35" t="s">
-        <v>375</v>
-      </c>
-      <c r="D111" s="35" t="s">
-        <v>378</v>
-      </c>
-      <c r="E111" s="39"/>
-      <c r="F111" s="35" t="s">
-        <v>377</v>
-      </c>
+      <c r="A111" s="89"/>
+      <c r="B111" s="99"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="37"/>
+      <c r="F111" s="36"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="88"/>
-      <c r="B112" s="101"/>
+      <c r="A112" s="89"/>
+      <c r="B112" s="91" t="s">
+        <v>327</v>
+      </c>
       <c r="C112" s="13" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="E112" s="33"/>
       <c r="F112" s="13" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="89"/>
+      <c r="B113" s="91"/>
+      <c r="C113" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="D113" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E113" s="33"/>
+      <c r="F113" s="13" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="88"/>
-      <c r="B113" s="102"/>
-      <c r="C113" s="36"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="37"/>
-      <c r="F113" s="36"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="88"/>
-      <c r="B114" s="91" t="s">
-        <v>331</v>
-      </c>
-      <c r="C114" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="E114" s="33"/>
-      <c r="F114" s="13" t="s">
-        <v>358</v>
-      </c>
+    <row r="114" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="93"/>
+      <c r="B114" s="92"/>
+      <c r="C114" s="40"/>
+      <c r="D114" s="40"/>
+      <c r="E114" s="41"/>
+      <c r="F114" s="40"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="88"/>
-      <c r="B115" s="91"/>
-      <c r="C115" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="E115" s="33"/>
-      <c r="F115" s="13" t="s">
+      <c r="A115" s="88" t="s">
+        <v>163</v>
+      </c>
+      <c r="B115" s="90" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D115" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="89"/>
+      <c r="B116" s="85"/>
+      <c r="C116" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F116" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="89"/>
+      <c r="B117" s="86"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="89"/>
+      <c r="B118" s="84" t="s">
+        <v>183</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F118" s="13" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="93"/>
-      <c r="B116" s="98"/>
-      <c r="C116" s="40"/>
-      <c r="D116" s="40"/>
-      <c r="E116" s="41"/>
-      <c r="F116" s="40"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="87" t="s">
-        <v>163</v>
-      </c>
-      <c r="B117" s="89" t="s">
-        <v>13</v>
-      </c>
-      <c r="C117" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="D117" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="E117" s="26"/>
-      <c r="F117" s="26" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="88"/>
-      <c r="B118" s="85"/>
-      <c r="C118" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="F118" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="88"/>
-      <c r="B119" s="86"/>
-      <c r="C119" s="36"/>
-      <c r="D119" s="36"/>
-      <c r="E119" s="36"/>
-      <c r="F119" s="36"/>
+      <c r="A119" s="89"/>
+      <c r="B119" s="85"/>
+      <c r="C119" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F119" s="13" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="88"/>
-      <c r="B120" s="84" t="s">
-        <v>183</v>
-      </c>
+      <c r="A120" s="89"/>
+      <c r="B120" s="85"/>
       <c r="C120" s="13" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F120" s="13" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="88"/>
+      <c r="A121" s="89"/>
       <c r="B121" s="85"/>
       <c r="C121" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>299</v>
+        <v>178</v>
       </c>
       <c r="F121" s="13" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="88"/>
+      <c r="A122" s="89"/>
       <c r="B122" s="85"/>
       <c r="C122" s="13" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F122" s="13" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="88"/>
+      <c r="A123" s="89"/>
       <c r="B123" s="85"/>
       <c r="C123" s="13" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F123" s="13" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="88"/>
-      <c r="B124" s="85"/>
-      <c r="C124" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F124" s="13" t="s">
-        <v>149</v>
-      </c>
+      <c r="A124" s="89"/>
+      <c r="B124" s="86"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="88"/>
-      <c r="B125" s="85"/>
-      <c r="C125" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="F125" s="13" t="s">
-        <v>149</v>
+      <c r="A125" s="89"/>
+      <c r="B125" s="84" t="s">
+        <v>206</v>
+      </c>
+      <c r="C125" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="D125" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="E125" s="35"/>
+      <c r="F125" s="35" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="88"/>
-      <c r="B126" s="86"/>
+      <c r="A126" s="89"/>
+      <c r="B126" s="85"/>
+      <c r="C126" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F126" s="13" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="88"/>
-      <c r="B127" s="84" t="s">
-        <v>206</v>
-      </c>
-      <c r="C127" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="D127" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="E127" s="35"/>
-      <c r="F127" s="35" t="s">
-        <v>208</v>
+      <c r="A127" s="89"/>
+      <c r="B127" s="85"/>
+      <c r="C127" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D127" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="F127" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="88"/>
+      <c r="A128" s="89"/>
       <c r="B128" s="85"/>
       <c r="C128" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F128" s="13" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="88"/>
+      <c r="A129" s="89"/>
       <c r="B129" s="85"/>
       <c r="C129" s="13" t="s">
-        <v>215</v>
+        <v>296</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>214</v>
+        <v>297</v>
       </c>
       <c r="F129" s="13" t="s">
-        <v>219</v>
+        <v>300</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="88"/>
+      <c r="A130" s="89"/>
       <c r="B130" s="85"/>
-      <c r="C130" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>209</v>
-      </c>
+      <c r="C130" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="D130" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="E130" s="44"/>
       <c r="F130" s="13" t="s">
-        <v>208</v>
+        <v>300</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="88"/>
+      <c r="A131" s="89"/>
       <c r="B131" s="85"/>
-      <c r="C131" s="13" t="s">
+      <c r="C131" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="D131" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="E131" s="44"/>
+      <c r="F131" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="D131" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="F131" s="13" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="88"/>
+      <c r="A132" s="89"/>
       <c r="B132" s="85"/>
-      <c r="C132" s="44" t="s">
-        <v>324</v>
-      </c>
-      <c r="D132" s="44" t="s">
-        <v>325</v>
-      </c>
-      <c r="E132" s="44"/>
+      <c r="C132" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>216</v>
+      </c>
       <c r="F132" s="13" t="s">
-        <v>304</v>
+        <v>218</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="88"/>
+      <c r="A133" s="89"/>
       <c r="B133" s="85"/>
-      <c r="C133" s="44" t="s">
-        <v>326</v>
-      </c>
-      <c r="D133" s="44" t="s">
-        <v>327</v>
-      </c>
-      <c r="E133" s="44"/>
+      <c r="C133" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="D133" s="13" t="s">
+        <v>211</v>
+      </c>
       <c r="F133" s="13" t="s">
-        <v>304</v>
+        <v>212</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="88"/>
+      <c r="A134" s="89"/>
       <c r="B134" s="85"/>
       <c r="C134" s="13" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F134" s="13" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="88"/>
+      <c r="A135" s="89"/>
       <c r="B135" s="85"/>
-      <c r="C135" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="F135" s="13" t="s">
+      <c r="C135" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="D135" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="E135" s="44"/>
+      <c r="F135" s="44" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="88"/>
+      <c r="A136" s="89"/>
       <c r="B136" s="85"/>
-      <c r="C136" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F136" s="13" t="s">
-        <v>212</v>
+      <c r="C136" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="D136" s="44" t="s">
+        <v>378</v>
+      </c>
+      <c r="E136" s="44"/>
+      <c r="F136" s="44" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="88"/>
+      <c r="A137" s="89"/>
       <c r="B137" s="85"/>
       <c r="C137" s="44" t="s">
-        <v>249</v>
+        <v>361</v>
       </c>
       <c r="D137" s="44" t="s">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="E137" s="44"/>
       <c r="F137" s="44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="88"/>
+      <c r="A138" s="89"/>
       <c r="B138" s="85"/>
       <c r="C138" s="44" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D138" s="44" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="E138" s="44"/>
       <c r="F138" s="44" t="s">
@@ -5399,165 +5387,121 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="88"/>
-      <c r="B139" s="85"/>
-      <c r="C139" s="44" t="s">
-        <v>365</v>
-      </c>
-      <c r="D139" s="44" t="s">
+      <c r="A139" s="89"/>
+      <c r="B139" s="86"/>
+      <c r="C139" s="44"/>
+      <c r="D139" s="44"/>
+      <c r="E139" s="44"/>
+      <c r="F139" s="44"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="89"/>
+      <c r="B140" s="84" t="s">
+        <v>222</v>
+      </c>
+      <c r="C140" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="D140" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="E140" s="35"/>
+      <c r="F140" s="35" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="89"/>
+      <c r="B141" s="85"/>
+      <c r="C141" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F141" s="13" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="89"/>
+      <c r="B142" s="85"/>
+      <c r="C142" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="F142" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="89"/>
+      <c r="B143" s="85"/>
+      <c r="C143" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="D143" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="E143" s="44"/>
+      <c r="F143" s="44" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="89"/>
+      <c r="B144" s="85"/>
+      <c r="C144" s="44" t="s">
+        <v>362</v>
+      </c>
+      <c r="D144" s="44" t="s">
+        <v>363</v>
+      </c>
+      <c r="E144" s="44"/>
+      <c r="F144" s="44" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="89"/>
+      <c r="B145" s="86"/>
+      <c r="C145" s="36"/>
+      <c r="D145" s="36"/>
+      <c r="E145" s="36"/>
+      <c r="F145" s="36"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="89"/>
+      <c r="B146" s="87" t="s">
+        <v>382</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="F146" s="13" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="89"/>
+      <c r="B147" s="87"/>
+      <c r="C147" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="E139" s="44"/>
-      <c r="F139" s="44" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="88"/>
-      <c r="B140" s="85"/>
-      <c r="C140" s="44" t="s">
-        <v>385</v>
-      </c>
-      <c r="D140" s="44" t="s">
-        <v>355</v>
-      </c>
-      <c r="E140" s="44"/>
-      <c r="F140" s="44" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="88"/>
-      <c r="B141" s="86"/>
-      <c r="C141" s="44"/>
-      <c r="D141" s="44"/>
-      <c r="E141" s="44"/>
-      <c r="F141" s="44"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="88"/>
-      <c r="B142" s="84" t="s">
-        <v>222</v>
-      </c>
-      <c r="C142" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="D142" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="E142" s="35"/>
-      <c r="F142" s="35" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="88"/>
-      <c r="B143" s="85"/>
-      <c r="C143" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="F143" s="13" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="88"/>
-      <c r="B144" s="85"/>
-      <c r="C144" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="F144" s="13" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="88"/>
-      <c r="B145" s="85"/>
-      <c r="C145" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="D145" s="44" t="s">
-        <v>252</v>
-      </c>
-      <c r="E145" s="44"/>
-      <c r="F145" s="44" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="88"/>
-      <c r="B146" s="85"/>
-      <c r="C146" s="44" t="s">
-        <v>366</v>
-      </c>
-      <c r="D146" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="E146" s="44"/>
-      <c r="F146" s="44" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="88"/>
-      <c r="B147" s="86"/>
-      <c r="C147" s="36"/>
-      <c r="D147" s="36"/>
-      <c r="E147" s="36"/>
-      <c r="F147" s="36"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="88"/>
-      <c r="B148" s="103" t="s">
+      <c r="D147" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="C148" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="F148" s="13" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="88"/>
-      <c r="B149" s="103"/>
-      <c r="C149" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="D149" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="F149" s="13" t="s">
-        <v>345</v>
+      <c r="F147" s="13" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A117:A149"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="B120:B126"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="A77:A99"/>
-    <mergeCell ref="B80:B89"/>
-    <mergeCell ref="B90:B99"/>
-    <mergeCell ref="A100:A116"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B111:B113"/>
     <mergeCell ref="A2:A44"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B23"/>
@@ -5567,6 +5511,22 @@
     <mergeCell ref="B24:B33"/>
     <mergeCell ref="B45:B54"/>
     <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="A77:A99"/>
+    <mergeCell ref="B80:B89"/>
+    <mergeCell ref="B90:B99"/>
+    <mergeCell ref="A100:A114"/>
+    <mergeCell ref="B100:B102"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="B109:B111"/>
+    <mergeCell ref="B140:B145"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A115:A147"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B125:B139"/>
+    <mergeCell ref="B118:B124"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5583,47 +5543,47 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="49" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="49" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="52" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="49" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="49" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="49" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="49" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="50" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="51" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
